--- a/Page_Bard/groups.xlsx
+++ b/Page_Bard/groups.xlsx
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C923"/>
+  <dimension ref="A1:C922"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="C616" s="12" t="inlineStr">
         <is>
-          <t>Барселона</t>
+          <t>Error_NoPostField</t>
         </is>
       </c>
     </row>
@@ -11415,12 +11415,12 @@
     <row r="670" ht="25" customHeight="1">
       <c r="A670" s="12" t="inlineStr">
         <is>
-          <t>[2252270111683147]</t>
+          <t>[689697483359428]</t>
         </is>
       </c>
       <c r="B670" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/2252270111683147И</t>
+          <t>https://www.facebook.com/groups/689697483359428</t>
         </is>
       </c>
       <c r="C670" s="12" t="inlineStr">
@@ -11432,29 +11432,29 @@
     <row r="671" ht="25" customHeight="1">
       <c r="A671" s="12" t="inlineStr">
         <is>
-          <t>[689697483359428]</t>
+          <t>[651383143230429]</t>
         </is>
       </c>
       <c r="B671" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/689697483359428</t>
+          <t>https://www.facebook.com/groups/651383143230429</t>
         </is>
       </c>
       <c r="C671" s="12" t="inlineStr">
         <is>
-          <t>Барселона</t>
+          <t>Ирландия</t>
         </is>
       </c>
     </row>
     <row r="672" ht="25" customHeight="1">
       <c r="A672" s="12" t="inlineStr">
         <is>
-          <t>[651383143230429]</t>
+          <t>[912905117375087]</t>
         </is>
       </c>
       <c r="B672" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/651383143230429</t>
+          <t>https://www.facebook.com/groups/912905117375087</t>
         </is>
       </c>
       <c r="C672" s="12" t="inlineStr">
@@ -11466,12 +11466,12 @@
     <row r="673" ht="25" customHeight="1">
       <c r="A673" s="12" t="inlineStr">
         <is>
-          <t>[912905117375087]</t>
+          <t>[1963652840322161]</t>
         </is>
       </c>
       <c r="B673" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/912905117375087</t>
+          <t>https://www.facebook.com/groups/1963652840322161</t>
         </is>
       </c>
       <c r="C673" s="12" t="inlineStr">
@@ -11481,31 +11481,31 @@
       </c>
     </row>
     <row r="674" ht="25" customHeight="1">
-      <c r="A674" s="12" t="inlineStr">
-        <is>
-          <t>[1963652840322161]</t>
-        </is>
-      </c>
-      <c r="B674" s="12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/1963652840322161</t>
-        </is>
-      </c>
-      <c r="C674" s="12" t="inlineStr">
-        <is>
-          <t>Ирландия</t>
+      <c r="A674" s="15" t="inlineStr">
+        <is>
+          <t>Я ♡ Аликанте</t>
+        </is>
+      </c>
+      <c r="B674" s="15" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/lucentum</t>
+        </is>
+      </c>
+      <c r="C674" s="15" t="inlineStr">
+        <is>
+          <t>Аликанте</t>
         </is>
       </c>
     </row>
     <row r="675" ht="25" customHeight="1">
       <c r="A675" s="15" t="inlineStr">
         <is>
-          <t>Я ♡ Аликанте</t>
+          <t>[815266519755987]</t>
         </is>
       </c>
       <c r="B675" s="15" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/lucentum</t>
+          <t>https://www.facebook.com/groups/815266519755987</t>
         </is>
       </c>
       <c r="C675" s="15" t="inlineStr">
@@ -11515,65 +11515,65 @@
       </c>
     </row>
     <row r="676" ht="25" customHeight="1">
-      <c r="A676" s="15" t="inlineStr">
-        <is>
-          <t>[815266519755987]</t>
-        </is>
-      </c>
-      <c r="B676" s="15" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/815266519755987</t>
-        </is>
-      </c>
-      <c r="C676" s="15" t="inlineStr">
-        <is>
-          <t>Аликанте</t>
+      <c r="A676" s="12" t="inlineStr">
+        <is>
+          <t>Русские встречи в Париже</t>
+        </is>
+      </c>
+      <c r="B676" s="12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1597838497137284</t>
+        </is>
+      </c>
+      <c r="C676" s="12" t="inlineStr">
+        <is>
+          <t>Париж</t>
         </is>
       </c>
     </row>
     <row r="677" ht="25" customHeight="1">
-      <c r="A677" s="12" t="inlineStr">
-        <is>
-          <t>Русские встречи в Париже</t>
-        </is>
-      </c>
-      <c r="B677" s="12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/1597838497137284</t>
-        </is>
-      </c>
-      <c r="C677" s="12" t="inlineStr">
+      <c r="A677" s="18" t="inlineStr">
+        <is>
+          <t>Мероприятия в Париже</t>
+        </is>
+      </c>
+      <c r="B677" s="18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/ruseventsinparis</t>
+        </is>
+      </c>
+      <c r="C677" s="18" t="inlineStr">
+        <is>
+          <t>Error_NoPostField</t>
+        </is>
+      </c>
+    </row>
+    <row r="678" ht="25" customHeight="1">
+      <c r="A678" s="12" t="inlineStr">
+        <is>
+          <t>RUSSIAN LIFE in PARIS</t>
+        </is>
+      </c>
+      <c r="B678" s="12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/83413646554</t>
+        </is>
+      </c>
+      <c r="C678" s="12" t="inlineStr">
         <is>
           <t>Париж</t>
-        </is>
-      </c>
-    </row>
-    <row r="678" ht="25" customHeight="1">
-      <c r="A678" s="18" t="inlineStr">
-        <is>
-          <t>Мероприятия в Париже</t>
-        </is>
-      </c>
-      <c r="B678" s="18" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/ruseventsinparis</t>
-        </is>
-      </c>
-      <c r="C678" s="18" t="inlineStr">
-        <is>
-          <t>Error_NoPostField</t>
         </is>
       </c>
     </row>
     <row r="679" ht="25" customHeight="1">
       <c r="A679" s="12" t="inlineStr">
         <is>
-          <t>RUSSIAN LIFE in PARIS</t>
+          <t>Русские в Париже - Russes à Paris - Russians in Paris</t>
         </is>
       </c>
       <c r="B679" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/83413646554</t>
+          <t>https://www.facebook.com/groups/400480280753701</t>
         </is>
       </c>
       <c r="C679" s="12" t="inlineStr">
@@ -11585,114 +11585,114 @@
     <row r="680" ht="25" customHeight="1">
       <c r="A680" s="12" t="inlineStr">
         <is>
-          <t>Русские в Париже - Russes à Paris - Russians in Paris</t>
+          <t>[chanson.russe]</t>
         </is>
       </c>
       <c r="B680" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/400480280753701</t>
+          <t>https://www.facebook.com/groups/chanson.russe</t>
         </is>
       </c>
       <c r="C680" s="12" t="inlineStr">
         <is>
-          <t>Париж</t>
+          <t>Франция</t>
         </is>
       </c>
     </row>
     <row r="681" ht="25" customHeight="1">
       <c r="A681" s="12" t="inlineStr">
         <is>
-          <t>[chanson.russe]</t>
+          <t>Наши бабушки в Париже</t>
         </is>
       </c>
       <c r="B681" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/chanson.russe</t>
+          <t>https://www.facebook.com/groups/177818129675104</t>
         </is>
       </c>
       <c r="C681" s="12" t="inlineStr">
         <is>
-          <t>Франция</t>
+          <t>Париж</t>
         </is>
       </c>
     </row>
     <row r="682" ht="25" customHeight="1">
       <c r="A682" s="12" t="inlineStr">
         <is>
-          <t>Наши бабушки в Париже</t>
+          <t>[329489834070016]</t>
         </is>
       </c>
       <c r="B682" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/177818129675104</t>
+          <t>https://www.facebook.com/groups/329489834070016</t>
         </is>
       </c>
       <c r="C682" s="12" t="inlineStr">
         <is>
+          <t>Франция</t>
+        </is>
+      </c>
+    </row>
+    <row r="683" ht="25" customHeight="1">
+      <c r="A683" s="18" t="inlineStr">
+        <is>
+          <t>[1618302348221481]</t>
+        </is>
+      </c>
+      <c r="B683" s="18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1618302348221481</t>
+        </is>
+      </c>
+      <c r="C683" s="18" t="inlineStr">
+        <is>
+          <t>Error_NoPostField</t>
+        </is>
+      </c>
+    </row>
+    <row r="684" ht="25" customHeight="1">
+      <c r="A684" s="12" t="inlineStr">
+        <is>
+          <t>Культурный код. Париж</t>
+        </is>
+      </c>
+      <c r="B684" s="12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/817559452098554</t>
+        </is>
+      </c>
+      <c r="C684" s="12" t="inlineStr">
+        <is>
           <t>Париж</t>
-        </is>
-      </c>
-    </row>
-    <row r="683" ht="25" customHeight="1">
-      <c r="A683" s="12" t="inlineStr">
-        <is>
-          <t>[329489834070016]</t>
-        </is>
-      </c>
-      <c r="B683" s="12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/329489834070016</t>
-        </is>
-      </c>
-      <c r="C683" s="12" t="inlineStr">
-        <is>
-          <t>Франция</t>
-        </is>
-      </c>
-    </row>
-    <row r="684" ht="25" customHeight="1">
-      <c r="A684" s="18" t="inlineStr">
-        <is>
-          <t>[1618302348221481]</t>
-        </is>
-      </c>
-      <c r="B684" s="18" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/1618302348221481</t>
-        </is>
-      </c>
-      <c r="C684" s="18" t="inlineStr">
-        <is>
-          <t>Error_NoPostField</t>
         </is>
       </c>
     </row>
     <row r="685" ht="25" customHeight="1">
       <c r="A685" s="12" t="inlineStr">
         <is>
-          <t>Культурный код. Париж</t>
+          <t>Русские во Франции ❤️ 🇫🇷 France / Франция</t>
         </is>
       </c>
       <c r="B685" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/817559452098554</t>
+          <t>https://www.facebook.com/groups/russian.france.ru</t>
         </is>
       </c>
       <c r="C685" s="12" t="inlineStr">
         <is>
-          <t>Париж</t>
+          <t>Франция</t>
         </is>
       </c>
     </row>
     <row r="686" ht="25" customHeight="1">
       <c r="A686" s="12" t="inlineStr">
         <is>
-          <t>Русские во Франции ❤️ 🇫🇷 France / Франция</t>
+          <t>Русские» во Франции</t>
         </is>
       </c>
       <c r="B686" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/russian.france.ru</t>
+          <t>https://www.facebook.com/groups/russkievofrancyi</t>
         </is>
       </c>
       <c r="C686" s="12" t="inlineStr">
@@ -11704,12 +11704,12 @@
     <row r="687" ht="25" customHeight="1">
       <c r="A687" s="12" t="inlineStr">
         <is>
-          <t>Русские» во Франции</t>
+          <t>Русскоязычные во Франции</t>
         </is>
       </c>
       <c r="B687" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/russkievofrancyi</t>
+          <t>https://www.facebook.com/groups/715382050454708</t>
         </is>
       </c>
       <c r="C687" s="12" t="inlineStr">
@@ -11719,65 +11719,65 @@
       </c>
     </row>
     <row r="688" ht="25" customHeight="1">
-      <c r="A688" s="12" t="inlineStr">
-        <is>
-          <t>Русскоязычные во Франции</t>
-        </is>
-      </c>
-      <c r="B688" s="12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/715382050454708</t>
-        </is>
-      </c>
-      <c r="C688" s="12" t="inlineStr">
-        <is>
-          <t>Франция</t>
+      <c r="A688" s="18" t="inlineStr">
+        <is>
+          <t>Наша Группа☀️🌴🌵 𐌓𐌓𐌓𐌓-𐌓𐌓𐌓! 🎭 Notre Groupe</t>
+        </is>
+      </c>
+      <c r="B688" s="18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/730924840621978</t>
+        </is>
+      </c>
+      <c r="C688" s="18" t="inlineStr">
+        <is>
+          <t>Error_NoPostField</t>
         </is>
       </c>
     </row>
     <row r="689" ht="25" customHeight="1">
-      <c r="A689" s="18" t="inlineStr">
-        <is>
-          <t>Наша Группа☀️🌴🌵 𐌓𐌓𐌓𐌓-𐌓𐌓𐌓! 🎭 Notre Groupe</t>
-        </is>
-      </c>
-      <c r="B689" s="18" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/730924840621978</t>
-        </is>
-      </c>
-      <c r="C689" s="18" t="inlineStr">
-        <is>
-          <t>Error_NoPostField</t>
+      <c r="A689" s="12" t="inlineStr">
+        <is>
+          <t>Русские в Париже</t>
+        </is>
+      </c>
+      <c r="B689" s="12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/paris.rus</t>
+        </is>
+      </c>
+      <c r="C689" s="12" t="inlineStr">
+        <is>
+          <t>Париж</t>
         </is>
       </c>
     </row>
     <row r="690" ht="25" customHeight="1">
       <c r="A690" s="12" t="inlineStr">
         <is>
-          <t>Русские в Париже</t>
+          <t>[1581276538632292]</t>
         </is>
       </c>
       <c r="B690" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/paris.rus</t>
+          <t>https://www.facebook.com/groups/1581276538632292</t>
         </is>
       </c>
       <c r="C690" s="12" t="inlineStr">
         <is>
-          <t>Париж</t>
+          <t>Франция</t>
         </is>
       </c>
     </row>
     <row r="691" ht="25" customHeight="1">
       <c r="A691" s="12" t="inlineStr">
         <is>
-          <t>[1581276538632292]</t>
+          <t>[russesfrance]</t>
         </is>
       </c>
       <c r="B691" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1581276538632292</t>
+          <t>https://www.facebook.com/groups/russesfrance</t>
         </is>
       </c>
       <c r="C691" s="12" t="inlineStr">
@@ -11789,63 +11789,63 @@
     <row r="692" ht="25" customHeight="1">
       <c r="A692" s="12" t="inlineStr">
         <is>
-          <t>[russesfrance]</t>
+          <t>Куплю-продам Русский Париж 💝💝💝💝</t>
         </is>
       </c>
       <c r="B692" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/russesfrance</t>
+          <t>https://www.facebook.com/groups/1744299435875508</t>
         </is>
       </c>
       <c r="C692" s="12" t="inlineStr">
         <is>
-          <t>Франция</t>
+          <t>Париж</t>
         </is>
       </c>
     </row>
     <row r="693" ht="25" customHeight="1">
       <c r="A693" s="12" t="inlineStr">
         <is>
-          <t>Куплю-продам Русский Париж 💝💝💝💝</t>
+          <t>Русскоязычные Во Франции</t>
         </is>
       </c>
       <c r="B693" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1744299435875508</t>
+          <t>https://www.facebook.com/groups/france.rus</t>
         </is>
       </c>
       <c r="C693" s="12" t="inlineStr">
         <is>
-          <t>Париж</t>
+          <t>Франция</t>
         </is>
       </c>
     </row>
     <row r="694" ht="25" customHeight="1">
-      <c r="A694" s="12" t="inlineStr">
-        <is>
-          <t>Русскоязычные Во Франции</t>
-        </is>
-      </c>
-      <c r="B694" s="12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/france.rus</t>
-        </is>
-      </c>
-      <c r="C694" s="12" t="inlineStr">
-        <is>
-          <t>Франция</t>
+      <c r="A694" s="18" t="inlineStr">
+        <is>
+          <t>Русскоязычные встречи в Париже</t>
+        </is>
+      </c>
+      <c r="B694" s="18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/541435772665366</t>
+        </is>
+      </c>
+      <c r="C694" s="18" t="inlineStr">
+        <is>
+          <t>Error_NoPostField</t>
         </is>
       </c>
     </row>
     <row r="695" ht="25" customHeight="1">
       <c r="A695" s="18" t="inlineStr">
         <is>
-          <t>Русскоязычные встречи в Париже</t>
+          <t>[687402491442221]</t>
         </is>
       </c>
       <c r="B695" s="18" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/541435772665366</t>
+          <t>https://www.facebook.com/groups/687402491442221</t>
         </is>
       </c>
       <c r="C695" s="18" t="inlineStr">
@@ -11855,31 +11855,31 @@
       </c>
     </row>
     <row r="696" ht="25" customHeight="1">
-      <c r="A696" s="18" t="inlineStr">
-        <is>
-          <t>[687402491442221]</t>
-        </is>
-      </c>
-      <c r="B696" s="18" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/687402491442221</t>
-        </is>
-      </c>
-      <c r="C696" s="18" t="inlineStr">
-        <is>
-          <t>Error_NoPostField</t>
+      <c r="A696" s="15" t="inlineStr">
+        <is>
+          <t>Русскоязычное сообщество Реховота</t>
+        </is>
+      </c>
+      <c r="B696" s="15" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1155171764531954</t>
+        </is>
+      </c>
+      <c r="C696" s="15" t="inlineStr">
+        <is>
+          <t>Реховот</t>
         </is>
       </c>
     </row>
     <row r="697" ht="25" customHeight="1">
       <c r="A697" s="15" t="inlineStr">
         <is>
-          <t>Русскоязычное сообщество Реховота</t>
+          <t>Реховот Альтернативный</t>
         </is>
       </c>
       <c r="B697" s="15" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1155171764531954</t>
+          <t>https://www.facebook.com/groups/RehovotAlternativa</t>
         </is>
       </c>
       <c r="C697" s="15" t="inlineStr">
@@ -11889,31 +11889,31 @@
       </c>
     </row>
     <row r="698" ht="25" customHeight="1">
-      <c r="A698" s="15" t="inlineStr">
-        <is>
-          <t>Реховот Альтернативный</t>
-        </is>
-      </c>
-      <c r="B698" s="15" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/RehovotAlternativa</t>
-        </is>
-      </c>
-      <c r="C698" s="15" t="inlineStr">
-        <is>
-          <t>Реховот</t>
+      <c r="A698" s="12" t="inlineStr">
+        <is>
+          <t>Русскоязычные объявления в Англии</t>
+        </is>
+      </c>
+      <c r="B698" s="12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/726881040779165</t>
+        </is>
+      </c>
+      <c r="C698" s="12" t="inlineStr">
+        <is>
+          <t>Лондон</t>
         </is>
       </c>
     </row>
     <row r="699" ht="25" customHeight="1">
       <c r="A699" s="12" t="inlineStr">
         <is>
-          <t>Русскоязычные объявления в Англии</t>
+          <t>Объявления в Лондоне</t>
         </is>
       </c>
       <c r="B699" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/726881040779165</t>
+          <t>https://www.facebook.com/groups/615502268141354</t>
         </is>
       </c>
       <c r="C699" s="12" t="inlineStr">
@@ -11925,12 +11925,12 @@
     <row r="700" ht="25" customHeight="1">
       <c r="A700" s="12" t="inlineStr">
         <is>
-          <t>Объявления в Лондоне</t>
+          <t>Реклама Лондон.</t>
         </is>
       </c>
       <c r="B700" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/615502268141354</t>
+          <t>https://www.facebook.com/groups/217344701931903</t>
         </is>
       </c>
       <c r="C700" s="12" t="inlineStr">
@@ -11942,12 +11942,12 @@
     <row r="701" ht="25" customHeight="1">
       <c r="A701" s="12" t="inlineStr">
         <is>
-          <t>Реклама Лондон.</t>
+          <t>Русские в Лондоне (Общаемся, Знакомимся)</t>
         </is>
       </c>
       <c r="B701" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/217344701931903</t>
+          <t>https://www.facebook.com/groups/russianslondon</t>
         </is>
       </c>
       <c r="C701" s="12" t="inlineStr">
@@ -11959,12 +11959,12 @@
     <row r="702" ht="25" customHeight="1">
       <c r="A702" s="12" t="inlineStr">
         <is>
-          <t>Русские в Лондоне (Общаемся, Знакомимся)</t>
+          <t>Лондон</t>
         </is>
       </c>
       <c r="B702" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/russianslondon</t>
+          <t>https://www.facebook.com/groups/ruslondon</t>
         </is>
       </c>
       <c r="C702" s="12" t="inlineStr">
@@ -11976,12 +11976,12 @@
     <row r="703" ht="25" customHeight="1">
       <c r="A703" s="12" t="inlineStr">
         <is>
-          <t>Лондон</t>
+          <t>ЛОНДОН ❤️ АНГЛИЯ ❤️ ВЕЛИКОБРИТАНИЯ</t>
         </is>
       </c>
       <c r="B703" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/ruslondon</t>
+          <t>https://www.facebook.com/groups/londonenglandgreatbritain</t>
         </is>
       </c>
       <c r="C703" s="12" t="inlineStr">
@@ -11993,12 +11993,12 @@
     <row r="704" ht="25" customHeight="1">
       <c r="A704" s="12" t="inlineStr">
         <is>
-          <t>ЛОНДОН ❤️ АНГЛИЯ ❤️ ВЕЛИКОБРИТАНИЯ</t>
+          <t>НашЧат - Лондон - Общение\Услуги\Объявления</t>
         </is>
       </c>
       <c r="B704" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/londonenglandgreatbritain</t>
+          <t>https://www.facebook.com/groups/nashchatlondon</t>
         </is>
       </c>
       <c r="C704" s="12" t="inlineStr">
@@ -12010,12 +12010,12 @@
     <row r="705" ht="25" customHeight="1">
       <c r="A705" s="12" t="inlineStr">
         <is>
-          <t>НашЧат - Лондон - Общение\Услуги\Объявления</t>
+          <t>Лондон для всех / London for all</t>
         </is>
       </c>
       <c r="B705" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/nashchatlondon</t>
+          <t>https://www.facebook.com/groups/698779930213566</t>
         </is>
       </c>
       <c r="C705" s="12" t="inlineStr">
@@ -12027,12 +12027,12 @@
     <row r="706" ht="25" customHeight="1">
       <c r="A706" s="12" t="inlineStr">
         <is>
-          <t>Лондон для всех / London for all</t>
+          <t>Доска объявлений в Лондоне</t>
         </is>
       </c>
       <c r="B706" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/698779930213566</t>
+          <t>https://www.facebook.com/groups/obyavleniyavlondone</t>
         </is>
       </c>
       <c r="C706" s="12" t="inlineStr">
@@ -12044,12 +12044,12 @@
     <row r="707" ht="25" customHeight="1">
       <c r="A707" s="12" t="inlineStr">
         <is>
-          <t>Доска объявлений в Лондоне</t>
+          <t>Русскоговорящие Лондона - Давай Дружить!</t>
         </is>
       </c>
       <c r="B707" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/obyavleniyavlondone</t>
+          <t>https://www.facebook.com/groups/russianspeakinglondoners</t>
         </is>
       </c>
       <c r="C707" s="12" t="inlineStr">
@@ -12061,12 +12061,12 @@
     <row r="708" ht="25" customHeight="1">
       <c r="A708" s="12" t="inlineStr">
         <is>
-          <t>Русскоговорящие Лондона - Давай Дружить!</t>
+          <t>Russian London / Русский Лондон</t>
         </is>
       </c>
       <c r="B708" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/russianspeakinglondoners</t>
+          <t>https://www.facebook.com/groups/russlanlondon</t>
         </is>
       </c>
       <c r="C708" s="12" t="inlineStr">
@@ -12078,12 +12078,12 @@
     <row r="709" ht="25" customHeight="1">
       <c r="A709" s="12" t="inlineStr">
         <is>
-          <t>Russian London / Русский Лондон</t>
+          <t>Доска Объявлений в Лондоне</t>
         </is>
       </c>
       <c r="B709" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/russlanlondon</t>
+          <t>https://www.facebook.com/groups/100601800429773</t>
         </is>
       </c>
       <c r="C709" s="12" t="inlineStr">
@@ -12095,12 +12095,12 @@
     <row r="710" ht="25" customHeight="1">
       <c r="A710" s="12" t="inlineStr">
         <is>
-          <t>Доска Объявлений в Лондоне</t>
+          <t>МЫ в Лондоне / UK</t>
         </is>
       </c>
       <c r="B710" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/100601800429773</t>
+          <t>https://www.facebook.com/groups/weinlondon</t>
         </is>
       </c>
       <c r="C710" s="12" t="inlineStr">
@@ -12112,29 +12112,29 @@
     <row r="711" ht="25" customHeight="1">
       <c r="A711" s="12" t="inlineStr">
         <is>
-          <t>МЫ в Лондоне / UK</t>
+          <t>Russians Events NL</t>
         </is>
       </c>
       <c r="B711" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/weinlondon</t>
+          <t>https://www.facebook.com/groups/111317319215160</t>
         </is>
       </c>
       <c r="C711" s="12" t="inlineStr">
         <is>
-          <t>Лондон</t>
+          <t>Роттердам</t>
         </is>
       </c>
     </row>
     <row r="712" ht="25" customHeight="1">
       <c r="A712" s="12" t="inlineStr">
         <is>
-          <t>Russians Events NL</t>
+          <t>Русскоязычные Роттердам, Нидерланды (Rotterdam, ...</t>
         </is>
       </c>
       <c r="B712" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/111317319215160</t>
+          <t>https://www.facebook.com/groups/1974215856487465</t>
         </is>
       </c>
       <c r="C712" s="12" t="inlineStr">
@@ -12146,29 +12146,29 @@
     <row r="713" ht="25" customHeight="1">
       <c r="A713" s="12" t="inlineStr">
         <is>
-          <t>Русскоязычные Роттердам, Нидерланды (Rotterdam, ...</t>
+          <t>Афиша в Нидерландах</t>
         </is>
       </c>
       <c r="B713" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1974215856487465</t>
+          <t>https://www.facebook.com/groups/657314071131585</t>
         </is>
       </c>
       <c r="C713" s="12" t="inlineStr">
         <is>
-          <t>Роттердам</t>
+          <t>Голландия</t>
         </is>
       </c>
     </row>
     <row r="714" ht="25" customHeight="1">
       <c r="A714" s="12" t="inlineStr">
         <is>
-          <t>Афиша в Нидерландах</t>
+          <t>Домашние концерты в Голландии и Бельгии</t>
         </is>
       </c>
       <c r="B714" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/657314071131585</t>
+          <t>https://www.facebook.com/groups/1573888439491304</t>
         </is>
       </c>
       <c r="C714" s="12" t="inlineStr">
@@ -12180,12 +12180,12 @@
     <row r="715" ht="25" customHeight="1">
       <c r="A715" s="12" t="inlineStr">
         <is>
-          <t>Домашние концерты в Голландии и Бельгии</t>
+          <t>Русские в Голландии - Russians in Holland</t>
         </is>
       </c>
       <c r="B715" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1573888439491304</t>
+          <t>https://www.facebook.com/groups/Russia.Netherlands</t>
         </is>
       </c>
       <c r="C715" s="12" t="inlineStr">
@@ -12195,48 +12195,48 @@
       </c>
     </row>
     <row r="716" ht="25" customHeight="1">
-      <c r="A716" s="12" t="inlineStr">
-        <is>
-          <t>Русские в Голландии - Russians in Holland</t>
-        </is>
-      </c>
-      <c r="B716" s="12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/Russia.Netherlands</t>
-        </is>
-      </c>
-      <c r="C716" s="12" t="inlineStr">
+      <c r="A716" s="18" t="inlineStr">
+        <is>
+          <t>Русскоязычные в Роттердаме</t>
+        </is>
+      </c>
+      <c r="B716" s="18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/712840965573831</t>
+        </is>
+      </c>
+      <c r="C716" s="18" t="inlineStr">
+        <is>
+          <t>Error_NoPostField</t>
+        </is>
+      </c>
+    </row>
+    <row r="717" ht="25" customHeight="1">
+      <c r="A717" s="12" t="inlineStr">
+        <is>
+          <t>Русские в Голландии</t>
+        </is>
+      </c>
+      <c r="B717" s="12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/776274652401336</t>
+        </is>
+      </c>
+      <c r="C717" s="12" t="inlineStr">
         <is>
           <t>Голландия</t>
-        </is>
-      </c>
-    </row>
-    <row r="717" ht="25" customHeight="1">
-      <c r="A717" s="18" t="inlineStr">
-        <is>
-          <t>Русскоязычные в Роттердаме</t>
-        </is>
-      </c>
-      <c r="B717" s="18" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/712840965573831</t>
-        </is>
-      </c>
-      <c r="C717" s="18" t="inlineStr">
-        <is>
-          <t>Error_NoPostField</t>
         </is>
       </c>
     </row>
     <row r="718" ht="25" customHeight="1">
       <c r="A718" s="12" t="inlineStr">
         <is>
-          <t>Русские в Голландии</t>
+          <t>[3025274331116207]</t>
         </is>
       </c>
       <c r="B718" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/776274652401336</t>
+          <t>https://www.facebook.com/groups/3025274331116207</t>
         </is>
       </c>
       <c r="C718" s="12" t="inlineStr">
@@ -12248,12 +12248,12 @@
     <row r="719" ht="25" customHeight="1">
       <c r="A719" s="12" t="inlineStr">
         <is>
-          <t>[3025274331116207]</t>
+          <t>[prostoobyavleniya]</t>
         </is>
       </c>
       <c r="B719" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/3025274331116207</t>
+          <t>https://www.facebook.com/groups/prostoobyavleniya</t>
         </is>
       </c>
       <c r="C719" s="12" t="inlineStr">
@@ -12265,12 +12265,12 @@
     <row r="720" ht="25" customHeight="1">
       <c r="A720" s="12" t="inlineStr">
         <is>
-          <t>[prostoobyavleniya]</t>
+          <t>[nl.reklama]</t>
         </is>
       </c>
       <c r="B720" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/prostoobyavleniya</t>
+          <t>https://www.facebook.com/groups/nl.reklama</t>
         </is>
       </c>
       <c r="C720" s="12" t="inlineStr">
@@ -12282,12 +12282,12 @@
     <row r="721" ht="25" customHeight="1">
       <c r="A721" s="12" t="inlineStr">
         <is>
-          <t>[nl.reklama]</t>
+          <t>[in.netherland]</t>
         </is>
       </c>
       <c r="B721" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/nl.reklama</t>
+          <t>https://www.facebook.com/groups/in.netherland</t>
         </is>
       </c>
       <c r="C721" s="12" t="inlineStr">
@@ -12299,29 +12299,29 @@
     <row r="722" ht="25" customHeight="1">
       <c r="A722" s="12" t="inlineStr">
         <is>
-          <t>[in.netherland]</t>
+          <t>РОТТЕРДАМ-НИДЕРЛАНДЫ</t>
         </is>
       </c>
       <c r="B722" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/in.netherland</t>
+          <t>https://www.facebook.com/groups/nederlandrotterdam</t>
         </is>
       </c>
       <c r="C722" s="12" t="inlineStr">
         <is>
-          <t>Голландия</t>
+          <t>Роттердам</t>
         </is>
       </c>
     </row>
     <row r="723" ht="25" customHeight="1">
       <c r="A723" s="12" t="inlineStr">
         <is>
-          <t>РОТТЕРДАМ-НИДЕРЛАНДЫ</t>
+          <t>Роттердам, Нидерланды (Rotterdam, Nederland)</t>
         </is>
       </c>
       <c r="B723" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/nederlandrotterdam</t>
+          <t>https://www.facebook.com/groups/rotterdamchat</t>
         </is>
       </c>
       <c r="C723" s="12" t="inlineStr">
@@ -12333,148 +12333,148 @@
     <row r="724" ht="25" customHeight="1">
       <c r="A724" s="12" t="inlineStr">
         <is>
-          <t>Роттердам, Нидерланды (Rotterdam, Nederland)</t>
+          <t>[3325441737705525]</t>
         </is>
       </c>
       <c r="B724" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/rotterdamchat</t>
+          <t>https://www.facebook.com/groups/3325441737705525</t>
         </is>
       </c>
       <c r="C724" s="12" t="inlineStr">
         <is>
-          <t>Роттердам</t>
+          <t>Голландия</t>
         </is>
       </c>
     </row>
     <row r="725" ht="25" customHeight="1">
       <c r="A725" s="12" t="inlineStr">
         <is>
-          <t>[3325441737705525]</t>
+          <t>Куда бы деться на Софаш</t>
         </is>
       </c>
       <c r="B725" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/3325441737705525</t>
+          <t>https://www.facebook.com/groups/sofash</t>
         </is>
       </c>
       <c r="C725" s="12" t="inlineStr">
         <is>
-          <t>Голландия</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
     <row r="726" ht="25" customHeight="1">
       <c r="A726" s="12" t="inlineStr">
         <is>
-          <t>Куда бы деться на Софаш</t>
+          <t>[netherlands2024]</t>
         </is>
       </c>
       <c r="B726" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/sofash</t>
+          <t>https://www.facebook.com/groups/netherlands2024</t>
         </is>
       </c>
       <c r="C726" s="12" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Голландия</t>
         </is>
       </c>
     </row>
     <row r="727" ht="25" customHeight="1">
       <c r="A727" s="12" t="inlineStr">
         <is>
-          <t>[netherlands2024]</t>
+          <t>[2014489635408191]</t>
         </is>
       </c>
       <c r="B727" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/netherlands2024</t>
+          <t>https://www.facebook.com/groups/2014489635408191</t>
         </is>
       </c>
       <c r="C727" s="12" t="inlineStr">
         <is>
-          <t>Голландия</t>
+          <t>Лимасол</t>
         </is>
       </c>
     </row>
     <row r="728" ht="25" customHeight="1">
       <c r="A728" s="12" t="inlineStr">
         <is>
-          <t>[2014489635408191]</t>
+          <t>[528187844004304]</t>
         </is>
       </c>
       <c r="B728" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/2014489635408191</t>
+          <t>https://www.facebook.com/groups/528187844004304</t>
         </is>
       </c>
       <c r="C728" s="12" t="inlineStr">
         <is>
-          <t>Лимасол</t>
+          <t>Франция</t>
         </is>
       </c>
     </row>
     <row r="729" ht="25" customHeight="1">
       <c r="A729" s="12" t="inlineStr">
         <is>
-          <t>[528187844004304]</t>
+          <t>[russkaja.estonia]</t>
         </is>
       </c>
       <c r="B729" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/528187844004304</t>
+          <t>https://www.facebook.com/groups/russkaja.estonia</t>
         </is>
       </c>
       <c r="C729" s="12" t="inlineStr">
         <is>
-          <t>Франция</t>
+          <t>Эстония</t>
         </is>
       </c>
     </row>
     <row r="730" ht="25" customHeight="1">
-      <c r="A730" s="12" t="inlineStr">
-        <is>
-          <t>[russkaja.estonia]</t>
-        </is>
-      </c>
-      <c r="B730" s="12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/russkaja.estonia</t>
-        </is>
-      </c>
-      <c r="C730" s="12" t="inlineStr">
-        <is>
-          <t>Эстония</t>
+      <c r="A730" s="18" t="inlineStr">
+        <is>
+          <t>Groups</t>
+        </is>
+      </c>
+      <c r="B730" s="18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/search/groups</t>
+        </is>
+      </c>
+      <c r="C730" s="18" t="inlineStr">
+        <is>
+          <t>Error_NoPostField</t>
         </is>
       </c>
     </row>
     <row r="731" ht="25" customHeight="1">
-      <c r="A731" s="18" t="inlineStr">
-        <is>
-          <t>Groups</t>
-        </is>
-      </c>
-      <c r="B731" s="18" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/search/groups</t>
-        </is>
-      </c>
-      <c r="C731" s="18" t="inlineStr">
-        <is>
-          <t>Error_NoPostField</t>
+      <c r="A731" s="12" t="inlineStr">
+        <is>
+          <t>Барахолка Нидерланды - " КУПЛЮ,ПРОДАМ,ОТДАМ "</t>
+        </is>
+      </c>
+      <c r="B731" s="12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1182506972341268</t>
+        </is>
+      </c>
+      <c r="C731" s="12" t="inlineStr">
+        <is>
+          <t>Голландия</t>
         </is>
       </c>
     </row>
     <row r="732" ht="25" customHeight="1">
       <c r="A732" s="12" t="inlineStr">
         <is>
-          <t>Барахолка Нидерланды - " КУПЛЮ,ПРОДАМ,ОТДАМ "</t>
+          <t>Послы красоты в Нидерландах</t>
         </is>
       </c>
       <c r="B732" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1182506972341268</t>
+          <t>https://www.facebook.com/groups/1146584646087973</t>
         </is>
       </c>
       <c r="C732" s="12" t="inlineStr">
@@ -12486,12 +12486,12 @@
     <row r="733" ht="25" customHeight="1">
       <c r="A733" s="12" t="inlineStr">
         <is>
-          <t>Послы красоты в Нидерландах</t>
+          <t>Русскоязычные голландцы / Russisch sprekende Nederlanders</t>
         </is>
       </c>
       <c r="B733" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1146584646087973</t>
+          <t>https://www.facebook.com/groups/342955332550205</t>
         </is>
       </c>
       <c r="C733" s="12" t="inlineStr">
@@ -12501,31 +12501,31 @@
       </c>
     </row>
     <row r="734" ht="25" customHeight="1">
-      <c r="A734" s="12" t="inlineStr">
-        <is>
-          <t>Русскоязычные голландцы / Russisch sprekende Nederlanders</t>
-        </is>
-      </c>
-      <c r="B734" s="12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/342955332550205</t>
-        </is>
-      </c>
-      <c r="C734" s="12" t="inlineStr">
-        <is>
-          <t>Голландия</t>
+      <c r="A734" s="18" t="inlineStr">
+        <is>
+          <t>Совет другу</t>
+        </is>
+      </c>
+      <c r="B734" s="18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/sovet.drugu</t>
+        </is>
+      </c>
+      <c r="C734" s="18" t="inlineStr">
+        <is>
+          <t>Error_NoPostField</t>
         </is>
       </c>
     </row>
     <row r="735" ht="25" customHeight="1">
       <c r="A735" s="18" t="inlineStr">
         <is>
-          <t>Совет другу</t>
+          <t>Выходцы из Украины в Нетании</t>
         </is>
       </c>
       <c r="B735" s="18" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/sovet.drugu</t>
+          <t>https://www.facebook.com/groups/ukr.netanya</t>
         </is>
       </c>
       <c r="C735" s="18" t="inlineStr">
@@ -12535,172 +12535,172 @@
       </c>
     </row>
     <row r="736" ht="25" customHeight="1">
-      <c r="A736" s="18" t="inlineStr">
-        <is>
-          <t>Выходцы из Украины в Нетании</t>
-        </is>
-      </c>
-      <c r="B736" s="18" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/ukr.netanya</t>
-        </is>
-      </c>
-      <c r="C736" s="18" t="inlineStr">
-        <is>
-          <t>Error_NoPostField</t>
+      <c r="A736" s="12" t="inlineStr">
+        <is>
+          <t>Моя и твоя Ирландия!</t>
+        </is>
+      </c>
+      <c r="B736" s="12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/779707795400787</t>
+        </is>
+      </c>
+      <c r="C736" s="12" t="inlineStr">
+        <is>
+          <t>Ирландия</t>
         </is>
       </c>
     </row>
     <row r="737" ht="25" customHeight="1">
       <c r="A737" s="12" t="inlineStr">
         <is>
-          <t>Моя и твоя Ирландия!</t>
+          <t>Роттердам - работа, жильё</t>
         </is>
       </c>
       <c r="B737" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/779707795400787</t>
+          <t>https://www.facebook.com/groups/jobs.rotterdam</t>
         </is>
       </c>
       <c r="C737" s="12" t="inlineStr">
         <is>
-          <t>Ирландия</t>
+          <t>Роттердам</t>
         </is>
       </c>
     </row>
     <row r="738" ht="25" customHeight="1">
       <c r="A738" s="12" t="inlineStr">
         <is>
-          <t>Роттердам - работа, жильё</t>
+          <t>ОБЪЯВЛЕНИЯ-Израиль, Север стра!</t>
         </is>
       </c>
       <c r="B738" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/jobs.rotterdam</t>
-        </is>
-      </c>
-      <c r="C738" s="12" t="inlineStr">
-        <is>
-          <t>Роттердам</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/groups/378725768994421</t>
+        </is>
+      </c>
+      <c r="C738" s="12" t="inlineStr"/>
     </row>
     <row r="739" ht="25" customHeight="1">
       <c r="A739" s="12" t="inlineStr">
         <is>
-          <t>ОБЪЯВЛЕНИЯ-Израиль, Север стра!</t>
+          <t>Русскоязычные встречи в Амстердаме и Голландии.</t>
         </is>
       </c>
       <c r="B739" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/378725768994421</t>
-        </is>
-      </c>
-      <c r="C739" s="12" t="inlineStr"/>
+          <t>https://www.facebook.com/groups/715400225520241</t>
+        </is>
+      </c>
+      <c r="C739" s="12" t="inlineStr">
+        <is>
+          <t>Голландия</t>
+        </is>
+      </c>
     </row>
     <row r="740" ht="25" customHeight="1">
-      <c r="A740" s="12" t="inlineStr">
-        <is>
-          <t>Русскоязычные встречи в Амстердаме и Голландии.</t>
-        </is>
-      </c>
-      <c r="B740" s="12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/715400225520241</t>
-        </is>
-      </c>
-      <c r="C740" s="12" t="inlineStr">
-        <is>
-          <t>Голландия</t>
+      <c r="A740" s="18" t="inlineStr">
+        <is>
+          <t>Голландия Жилье Квартиры Дома Аренда Амстердам Сеть Помогаем Нашим!</t>
+        </is>
+      </c>
+      <c r="B740" s="18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/pn.netherlands.hm</t>
+        </is>
+      </c>
+      <c r="C740" s="18" t="inlineStr">
+        <is>
+          <t>Error_NoPostField</t>
         </is>
       </c>
     </row>
     <row r="741" ht="25" customHeight="1">
-      <c r="A741" s="18" t="inlineStr">
-        <is>
-          <t>Голландия Жилье Квартиры Дома Аренда Амстердам Сеть Помогаем Нашим!</t>
-        </is>
-      </c>
-      <c r="B741" s="18" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/pn.netherlands.hm</t>
-        </is>
-      </c>
-      <c r="C741" s="18" t="inlineStr">
+      <c r="A741" s="12" t="inlineStr">
+        <is>
+          <t>Репатрианты в Израиле: здесь помогают и делятся опытом</t>
+        </is>
+      </c>
+      <c r="B741" s="12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/repatrianty</t>
+        </is>
+      </c>
+      <c r="C741" s="12" t="inlineStr"/>
+    </row>
+    <row r="742" ht="25" customHeight="1">
+      <c r="A742" s="18" t="inlineStr">
+        <is>
+          <t>Талантливые люди ищут работу</t>
+        </is>
+      </c>
+      <c r="B742" s="18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1522757981756335</t>
+        </is>
+      </c>
+      <c r="C742" s="18" t="inlineStr">
         <is>
           <t>Error_NoPostField</t>
         </is>
       </c>
     </row>
-    <row r="742" ht="25" customHeight="1">
-      <c r="A742" s="12" t="inlineStr">
-        <is>
-          <t>Репатрианты в Израиле: здесь помогают и делятся опытом</t>
-        </is>
-      </c>
-      <c r="B742" s="12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/repatrianty</t>
-        </is>
-      </c>
-      <c r="C742" s="12" t="inlineStr"/>
-    </row>
     <row r="743" ht="25" customHeight="1">
-      <c r="A743" s="18" t="inlineStr">
-        <is>
-          <t>Талантливые люди ищут работу</t>
-        </is>
-      </c>
-      <c r="B743" s="18" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/1522757981756335</t>
-        </is>
-      </c>
-      <c r="C743" s="18" t="inlineStr">
-        <is>
-          <t>Error_NoPostField</t>
-        </is>
-      </c>
+      <c r="A743" s="12" t="inlineStr">
+        <is>
+          <t>דרושים דוברי רוסית! Работы для русскоговорящих в Израиле</t>
+        </is>
+      </c>
+      <c r="B743" s="12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/4367146446659699</t>
+        </is>
+      </c>
+      <c r="C743" s="12" t="inlineStr"/>
     </row>
     <row r="744" ht="25" customHeight="1">
       <c r="A744" s="12" t="inlineStr">
         <is>
-          <t>דרושים דוברי רוסית! Работы для русскоговорящих в Израиле</t>
+          <t>Голландия Нидерланды  Работа,Жильё,Куплю,Продам,Объявления.</t>
         </is>
       </c>
       <c r="B744" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/4367146446659699</t>
-        </is>
-      </c>
-      <c r="C744" s="12" t="inlineStr"/>
+          <t>https://www.facebook.com/groups/992845460780330</t>
+        </is>
+      </c>
+      <c r="C744" s="12" t="inlineStr">
+        <is>
+          <t>Голландия</t>
+        </is>
+      </c>
     </row>
     <row r="745" ht="25" customHeight="1">
       <c r="A745" s="12" t="inlineStr">
         <is>
-          <t>Голландия Нидерланды  Работа,Жильё,Куплю,Продам,Объявления.</t>
+          <t>ЗНАКОМСТВА НИДЕРЛАНДЫ Амстердам Роттердам Гаага Эйндховен Бреда Арнем Снек</t>
         </is>
       </c>
       <c r="B745" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/992845460780330</t>
+          <t>https://www.facebook.com/groups/710502407350938</t>
         </is>
       </c>
       <c r="C745" s="12" t="inlineStr">
         <is>
-          <t>Голландия</t>
+          <t>Роттердам</t>
         </is>
       </c>
     </row>
     <row r="746" ht="25" customHeight="1">
       <c r="A746" s="12" t="inlineStr">
         <is>
-          <t>ЗНАКОМСТВА НИДЕРЛАНДЫ Амстердам Роттердам Гаага Эйндховен Бреда Арнем Снек</t>
+          <t>БЕСПЛАТНЫЕ ОБЪЯВЛЕНИЯ Голландия (Нидерланды) Амстердам Роттердам Гаага</t>
         </is>
       </c>
       <c r="B746" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/710502407350938</t>
+          <t>https://www.facebook.com/groups/283903809374845</t>
         </is>
       </c>
       <c r="C746" s="12" t="inlineStr">
@@ -12710,31 +12710,31 @@
       </c>
     </row>
     <row r="747" ht="25" customHeight="1">
-      <c r="A747" s="12" t="inlineStr">
-        <is>
-          <t>БЕСПЛАТНЫЕ ОБЪЯВЛЕНИЯ Голландия (Нидерланды) Амстердам Роттердам Гаага</t>
-        </is>
-      </c>
-      <c r="B747" s="12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/283903809374845</t>
-        </is>
-      </c>
-      <c r="C747" s="12" t="inlineStr">
-        <is>
-          <t>Роттердам</t>
+      <c r="A747" s="18" t="inlineStr">
+        <is>
+          <t>Живые встречи в Роттердаме</t>
+        </is>
+      </c>
+      <c r="B747" s="18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/679299362568960</t>
+        </is>
+      </c>
+      <c r="C747" s="18" t="inlineStr">
+        <is>
+          <t>Error_NoPostField</t>
         </is>
       </c>
     </row>
     <row r="748" ht="25" customHeight="1">
       <c r="A748" s="18" t="inlineStr">
         <is>
-          <t>Живые встречи в Роттердаме</t>
+          <t>Девочки Роттердама</t>
         </is>
       </c>
       <c r="B748" s="18" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/679299362568960</t>
+          <t>https://www.facebook.com/groups/devochkirotterdama</t>
         </is>
       </c>
       <c r="C748" s="18" t="inlineStr">
@@ -12744,31 +12744,31 @@
       </c>
     </row>
     <row r="749" ht="25" customHeight="1">
-      <c r="A749" s="18" t="inlineStr">
-        <is>
-          <t>Девочки Роттердама</t>
-        </is>
-      </c>
-      <c r="B749" s="18" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/devochkirotterdama</t>
-        </is>
-      </c>
-      <c r="C749" s="18" t="inlineStr">
-        <is>
-          <t>Error_NoPostField</t>
+      <c r="A749" s="12" t="inlineStr">
+        <is>
+          <t>Объявления в Голландии (Амстердам, Роттердам, Гаага, Утрехт, Эйндховен</t>
+        </is>
+      </c>
+      <c r="B749" s="12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/netherlandseueu</t>
+        </is>
+      </c>
+      <c r="C749" s="12" t="inlineStr">
+        <is>
+          <t>Роттердам</t>
         </is>
       </c>
     </row>
     <row r="750" ht="25" customHeight="1">
       <c r="A750" s="12" t="inlineStr">
         <is>
-          <t>Объявления в Голландии (Амстердам, Роттердам, Гаага, Утрехт, Эйндховен</t>
+          <t>РАБОТА НИДЕРЛАНДЫ(Голландия) Амстердам Роттердам Гаага Утрехт Эйндховен</t>
         </is>
       </c>
       <c r="B750" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/netherlandseueu</t>
+          <t>https://www.facebook.com/groups/174488348514688</t>
         </is>
       </c>
       <c r="C750" s="12" t="inlineStr">
@@ -12780,59 +12780,59 @@
     <row r="751" ht="25" customHeight="1">
       <c r="A751" s="12" t="inlineStr">
         <is>
-          <t>РАБОТА НИДЕРЛАНДЫ(Голландия) Амстердам Роттердам Гаага Утрехт Эйндховен</t>
+          <t>Наша Голландїя</t>
         </is>
       </c>
       <c r="B751" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/174488348514688</t>
+          <t>https://www.facebook.com/groups/nashagollandia</t>
         </is>
       </c>
       <c r="C751" s="12" t="inlineStr">
         <is>
-          <t>Роттердам</t>
+          <t>Голландия</t>
         </is>
       </c>
     </row>
     <row r="752" ht="25" customHeight="1">
       <c r="A752" s="12" t="inlineStr">
         <is>
-          <t>Наша Голландїя</t>
+          <t>РАБОТА! АШДОД И   ВЕСЬ  ИЗРИЛЬדרושים! אשדוד וכול הארץ !</t>
         </is>
       </c>
       <c r="B752" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/nashagollandia</t>
-        </is>
-      </c>
-      <c r="C752" s="12" t="inlineStr">
-        <is>
-          <t>Голландия</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/groups/2029142084035126</t>
+        </is>
+      </c>
+      <c r="C752" s="12" t="inlineStr"/>
     </row>
     <row r="753" ht="25" customHeight="1">
-      <c r="A753" s="12" t="inlineStr">
-        <is>
-          <t>РАБОТА! АШДОД И   ВЕСЬ  ИЗРИЛЬדרושים! אשדוד וכול הארץ !</t>
-        </is>
-      </c>
-      <c r="B753" s="12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/2029142084035126</t>
-        </is>
-      </c>
-      <c r="C753" s="12" t="inlineStr"/>
+      <c r="A753" s="18" t="inlineStr">
+        <is>
+          <t>Українці ❘ Роттердам, Нідерланди (Oekraïners ❘ Rotterdam, Nederland)</t>
+        </is>
+      </c>
+      <c r="B753" s="18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/ukrainiansrotterdam</t>
+        </is>
+      </c>
+      <c r="C753" s="18" t="inlineStr">
+        <is>
+          <t>Error_NoPostField</t>
+        </is>
+      </c>
     </row>
     <row r="754" ht="25" customHeight="1">
       <c r="A754" s="18" t="inlineStr">
         <is>
-          <t>Українці ❘ Роттердам, Нідерланди (Oekraïners ❘ Rotterdam, Nederland)</t>
+          <t>Ukrainians in Rotterdam/Українці в Роттердамі</t>
         </is>
       </c>
       <c r="B754" s="18" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/ukrainiansrotterdam</t>
+          <t>https://www.facebook.com/groups/uainrotterdam</t>
         </is>
       </c>
       <c r="C754" s="18" t="inlineStr">
@@ -12844,12 +12844,12 @@
     <row r="755" ht="25" customHeight="1">
       <c r="A755" s="18" t="inlineStr">
         <is>
-          <t>Ukrainians in Rotterdam/Українці в Роттердамі</t>
+          <t>Українці в Нідерландах / Робота Нідерланди / Амстердам Роттердам Гаага</t>
         </is>
       </c>
       <c r="B755" s="18" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/uainrotterdam</t>
+          <t>https://www.facebook.com/groups/ukrainiansandnetherlands</t>
         </is>
       </c>
       <c r="C755" s="18" t="inlineStr">
@@ -12861,12 +12861,12 @@
     <row r="756" ht="25" customHeight="1">
       <c r="A756" s="18" t="inlineStr">
         <is>
-          <t>Українці в Нідерландах / Робота Нідерланди / Амстердам Роттердам Гаага</t>
+          <t>Українці в Нідерландах (Роттердам, Амстердам, Гаага, Утрехт, Ейндховен)</t>
         </is>
       </c>
       <c r="B756" s="18" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/ukrainiansandnetherlands</t>
+          <t>https://www.facebook.com/groups/uanetherlands</t>
         </is>
       </c>
       <c r="C756" s="18" t="inlineStr">
@@ -12878,12 +12878,12 @@
     <row r="757" ht="25" customHeight="1">
       <c r="A757" s="18" t="inlineStr">
         <is>
-          <t>Українці в Нідерландах (Роттердам, Амстердам, Гаага, Утрехт, Ейндховен)</t>
+          <t>УКРАЇНЦІ в Роттердам / Гаага / Амстердам / Вакансії / Оголошення / Інше</t>
         </is>
       </c>
       <c r="B757" s="18" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/uanetherlands</t>
+          <t>https://www.facebook.com/groups/ukrainiansinrotterdamthehagueamsterdam</t>
         </is>
       </c>
       <c r="C757" s="18" t="inlineStr">
@@ -12895,12 +12895,12 @@
     <row r="758" ht="25" customHeight="1">
       <c r="A758" s="18" t="inlineStr">
         <is>
-          <t>УКРАЇНЦІ в Роттердам / Гаага / Амстердам / Вакансії / Оголошення / Інше</t>
+          <t>Роттердам по-нашому, Українці в Нідерландах (Oekraïners in Rotterdam)</t>
         </is>
       </c>
       <c r="B758" s="18" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/ukrainiansinrotterdamthehagueamsterdam</t>
+          <t>https://www.facebook.com/groups/1120620832601597</t>
         </is>
       </c>
       <c r="C758" s="18" t="inlineStr">
@@ -12912,12 +12912,12 @@
     <row r="759" ht="25" customHeight="1">
       <c r="A759" s="18" t="inlineStr">
         <is>
-          <t>Роттердам по-нашому, Українці в Нідерландах (Oekraïners in Rotterdam)</t>
+          <t>Українці в Нідерландах Амстердам, Ротердам, Гаага, Лейден, Утрехт</t>
         </is>
       </c>
       <c r="B759" s="18" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1120620832601597</t>
+          <t>https://www.facebook.com/groups/864663328149828</t>
         </is>
       </c>
       <c r="C759" s="18" t="inlineStr">
@@ -12929,12 +12929,12 @@
     <row r="760" ht="25" customHeight="1">
       <c r="A760" s="18" t="inlineStr">
         <is>
-          <t>Українці в Нідерландах Амстердам, Ротердам, Гаага, Лейден, Утрехт</t>
+          <t>Жильё в Нидерландах для украинцев Гага, Амстердам. Роттердам.</t>
         </is>
       </c>
       <c r="B760" s="18" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/864663328149828</t>
+          <t>https://www.facebook.com/groups/725299306742821</t>
         </is>
       </c>
       <c r="C760" s="18" t="inlineStr">
@@ -12944,31 +12944,27 @@
       </c>
     </row>
     <row r="761" ht="25" customHeight="1">
-      <c r="A761" s="18" t="inlineStr">
-        <is>
-          <t>Жильё в Нидерландах для украинцев Гага, Амстердам. Роттердам.</t>
-        </is>
-      </c>
-      <c r="B761" s="18" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/725299306742821</t>
-        </is>
-      </c>
-      <c r="C761" s="18" t="inlineStr">
-        <is>
-          <t>Error_NoPostField</t>
-        </is>
-      </c>
+      <c r="A761" s="12" t="inlineStr">
+        <is>
+          <t>🇮🇱 Израиль | Работа | Куплю-Продам | Аренда | Услуги | Реклама</t>
+        </is>
+      </c>
+      <c r="B761" s="12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1838179303126378</t>
+        </is>
+      </c>
+      <c r="C761" s="12" t="inlineStr"/>
     </row>
     <row r="762" ht="25" customHeight="1">
       <c r="A762" s="12" t="inlineStr">
         <is>
-          <t>🇮🇱 Израиль | Работа | Куплю-Продам | Аренда | Услуги | Реклама</t>
+          <t>Бесплатная доска объявлений в Израиле</t>
         </is>
       </c>
       <c r="B762" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1838179303126378</t>
+          <t>https://www.facebook.com/groups/824579077585876</t>
         </is>
       </c>
       <c r="C762" s="12" t="inlineStr"/>
@@ -12976,12 +12972,12 @@
     <row r="763" ht="25" customHeight="1">
       <c r="A763" s="12" t="inlineStr">
         <is>
-          <t>Бесплатная доска объявлений в Израиле</t>
+          <t>Ришон-ле-Цион 🇮🇱 Объявления 🇮🇱 Реклама</t>
         </is>
       </c>
       <c r="B763" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/824579077585876</t>
+          <t>https://www.facebook.com/groups/939016383659342</t>
         </is>
       </c>
       <c r="C763" s="12" t="inlineStr"/>
@@ -12989,12 +12985,12 @@
     <row r="764" ht="25" customHeight="1">
       <c r="A764" s="12" t="inlineStr">
         <is>
-          <t>Ришон-ле-Цион 🇮🇱 Объявления 🇮🇱 Реклама</t>
+          <t>ДОСКА ОБЪЯВЛЕНИЙ - НАШ ИЗРАИЛЬ</t>
         </is>
       </c>
       <c r="B764" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/939016383659342</t>
+          <t>https://www.facebook.com/groups/967693269960509</t>
         </is>
       </c>
       <c r="C764" s="12" t="inlineStr"/>
@@ -13002,12 +12998,12 @@
     <row r="765" ht="25" customHeight="1">
       <c r="A765" s="12" t="inlineStr">
         <is>
-          <t>ДОСКА ОБЪЯВЛЕНИЙ - НАШ ИЗРАИЛЬ</t>
+          <t>Нагария » Доска объявлений Израиля</t>
         </is>
       </c>
       <c r="B765" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/967693269960509</t>
+          <t>https://www.facebook.com/groups/NahariyaBoard</t>
         </is>
       </c>
       <c r="C765" s="12" t="inlineStr"/>
@@ -13015,12 +13011,12 @@
     <row r="766" ht="25" customHeight="1">
       <c r="A766" s="12" t="inlineStr">
         <is>
-          <t>Нагария » Доска объявлений Израиля</t>
+          <t>Базар Хайфы, Крайот и соседей</t>
         </is>
       </c>
       <c r="B766" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/NahariyaBoard</t>
+          <t>https://www.facebook.com/groups/275637809583928</t>
         </is>
       </c>
       <c r="C766" s="12" t="inlineStr"/>
@@ -13028,12 +13024,12 @@
     <row r="767" ht="25" customHeight="1">
       <c r="A767" s="12" t="inlineStr">
         <is>
-          <t>Базар Хайфы, Крайот и соседей</t>
+          <t>Реклама- Хайфа, Крайоты, Нешер, Тират-Кармель</t>
         </is>
       </c>
       <c r="B767" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/275637809583928</t>
+          <t>https://www.facebook.com/groups/710232390572120</t>
         </is>
       </c>
       <c r="C767" s="12" t="inlineStr"/>
@@ -13041,12 +13037,12 @@
     <row r="768" ht="25" customHeight="1">
       <c r="A768" s="12" t="inlineStr">
         <is>
-          <t>Реклама- Хайфа, Крайоты, Нешер, Тират-Кармель</t>
+          <t>Израильская доска бесплатных объявлений</t>
         </is>
       </c>
       <c r="B768" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/710232390572120</t>
+          <t>https://www.facebook.com/groups/isradoska</t>
         </is>
       </c>
       <c r="C768" s="12" t="inlineStr"/>
@@ -13054,12 +13050,12 @@
     <row r="769" ht="25" customHeight="1">
       <c r="A769" s="12" t="inlineStr">
         <is>
-          <t>Израильская доска бесплатных объявлений</t>
+          <t>Наш город Ришон Ле Цион . Недвижимость/ куплю/ продам / поменяю / услуги/</t>
         </is>
       </c>
       <c r="B769" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/isradoska</t>
+          <t>https://www.facebook.com/groups/1949421335330596</t>
         </is>
       </c>
       <c r="C769" s="12" t="inlineStr"/>
@@ -13067,12 +13063,12 @@
     <row r="770" ht="25" customHeight="1">
       <c r="A770" s="12" t="inlineStr">
         <is>
-          <t>Наш город Ришон Ле Цион . Недвижимость/ куплю/ продам / поменяю / услуги/</t>
+          <t>Haifa,крайот,Нешер,Тира-реклама,обьявления,куплю ,продам,отдам даром.</t>
         </is>
       </c>
       <c r="B770" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1949421335330596</t>
+          <t>https://www.facebook.com/groups/1436924709954737</t>
         </is>
       </c>
       <c r="C770" s="12" t="inlineStr"/>
@@ -13080,12 +13076,12 @@
     <row r="771" ht="25" customHeight="1">
       <c r="A771" s="12" t="inlineStr">
         <is>
-          <t>Haifa,крайот,Нешер,Тира-реклама,обьявления,куплю ,продам,отдам даром.</t>
+          <t>Бесплатная Реклама Израиль</t>
         </is>
       </c>
       <c r="B771" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1436924709954737</t>
+          <t>https://www.facebook.com/groups/902092163289858</t>
         </is>
       </c>
       <c r="C771" s="12" t="inlineStr"/>
@@ -13093,12 +13089,12 @@
     <row r="772" ht="25" customHeight="1">
       <c r="A772" s="12" t="inlineStr">
         <is>
-          <t>Бесплатная Реклама Израиль</t>
+          <t>Куплю / продам. Доска объявлений по Ашдоду.</t>
         </is>
       </c>
       <c r="B772" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/902092163289858</t>
+          <t>https://www.facebook.com/groups/190529101460106</t>
         </is>
       </c>
       <c r="C772" s="12" t="inlineStr"/>
@@ -13106,12 +13102,12 @@
     <row r="773" ht="25" customHeight="1">
       <c r="A773" s="12" t="inlineStr">
         <is>
-          <t>Куплю / продам. Доска объявлений по Ашдоду.</t>
+          <t>Север »  Доска объявлений Израиля</t>
         </is>
       </c>
       <c r="B773" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/190529101460106</t>
+          <t>https://www.facebook.com/groups/Northofisrael</t>
         </is>
       </c>
       <c r="C773" s="12" t="inlineStr"/>
@@ -13119,12 +13115,12 @@
     <row r="774" ht="25" customHeight="1">
       <c r="A774" s="12" t="inlineStr">
         <is>
-          <t>Север »  Доска объявлений Израиля</t>
+          <t>🎯Барахолка Беер Шева - Доска объявлений</t>
         </is>
       </c>
       <c r="B774" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/Northofisrael</t>
+          <t>https://www.facebook.com/groups/baraholka.BeerSheva</t>
         </is>
       </c>
       <c r="C774" s="12" t="inlineStr"/>
@@ -13132,12 +13128,12 @@
     <row r="775" ht="25" customHeight="1">
       <c r="A775" s="12" t="inlineStr">
         <is>
-          <t>🎯Барахолка Беер Шева - Доска объявлений</t>
+          <t>наша нагария:отдам,продам,куплю,предложения о работе ......</t>
         </is>
       </c>
       <c r="B775" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/baraholka.BeerSheva</t>
+          <t>https://www.facebook.com/groups/2148814295330105</t>
         </is>
       </c>
       <c r="C775" s="12" t="inlineStr"/>
@@ -13145,12 +13141,12 @@
     <row r="776" ht="25" customHeight="1">
       <c r="A776" s="12" t="inlineStr">
         <is>
-          <t>наша нагария:отдам,продам,куплю,предложения о работе ......</t>
+          <t>Беер Шева и Негев - Все вместе! באר שבע והסביבה כולם יחד</t>
         </is>
       </c>
       <c r="B776" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/2148814295330105</t>
+          <t>https://www.facebook.com/groups/208611776417778</t>
         </is>
       </c>
       <c r="C776" s="12" t="inlineStr"/>
@@ -13158,12 +13154,12 @@
     <row r="777" ht="25" customHeight="1">
       <c r="A777" s="12" t="inlineStr">
         <is>
-          <t>Беер Шева и Негев - Все вместе! באר שבע והסביבה כולם יחד</t>
+          <t>ДОСКА ОБЪЯВЛЕНИЙ МОЙ ИЗРАИЛЬ МОЯ СТРАНА</t>
         </is>
       </c>
       <c r="B777" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/208611776417778</t>
+          <t>https://www.facebook.com/groups/1140753995983976</t>
         </is>
       </c>
       <c r="C777" s="12" t="inlineStr"/>
@@ -13171,12 +13167,12 @@
     <row r="778" ht="25" customHeight="1">
       <c r="A778" s="12" t="inlineStr">
         <is>
-          <t>ДОСКА ОБЪЯВЛЕНИЙ МОЙ ИЗРАИЛЬ МОЯ СТРАНА</t>
+          <t>Ашкелон по другому.</t>
         </is>
       </c>
       <c r="B778" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1140753995983976</t>
+          <t>https://www.facebook.com/groups/1525240427701750</t>
         </is>
       </c>
       <c r="C778" s="12" t="inlineStr"/>
@@ -13184,12 +13180,12 @@
     <row r="779" ht="25" customHeight="1">
       <c r="A779" s="12" t="inlineStr">
         <is>
-          <t>Ашкелон по другому.</t>
+          <t>Ашдодцы для Ашдода  אשדודים למען אשדוד</t>
         </is>
       </c>
       <c r="B779" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1525240427701750</t>
+          <t>https://www.facebook.com/groups/389687825431277</t>
         </is>
       </c>
       <c r="C779" s="12" t="inlineStr"/>
@@ -13197,12 +13193,12 @@
     <row r="780" ht="25" customHeight="1">
       <c r="A780" s="12" t="inlineStr">
         <is>
-          <t>Ашдодцы для Ашдода  אשדודים למען אשדוד</t>
+          <t>Беэр Шева - Доска полезных объявлений - ADS board Beer Sheva - באר שבע</t>
         </is>
       </c>
       <c r="B780" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/389687825431277</t>
+          <t>https://www.facebook.com/groups/mybeersheva</t>
         </is>
       </c>
       <c r="C780" s="12" t="inlineStr"/>
@@ -13210,12 +13206,12 @@
     <row r="781" ht="25" customHeight="1">
       <c r="A781" s="12" t="inlineStr">
         <is>
-          <t>Беэр Шева - Доска полезных объявлений - ADS board Beer Sheva - באר שבע</t>
+          <t>Ашдод-אשדוד,объявления,продажа,покупка</t>
         </is>
       </c>
       <c r="B781" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/mybeersheva</t>
+          <t>https://www.facebook.com/groups/399317391008928</t>
         </is>
       </c>
       <c r="C781" s="12" t="inlineStr"/>
@@ -13223,12 +13219,12 @@
     <row r="782" ht="25" customHeight="1">
       <c r="A782" s="12" t="inlineStr">
         <is>
-          <t>Ашдод-אשדוד,объявления,продажа,покупка</t>
+          <t>✏ Работа и услуги в Нетания ⒿⓄⒷ</t>
         </is>
       </c>
       <c r="B782" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/399317391008928</t>
+          <t>https://www.facebook.com/groups/JobNetaniyaRus</t>
         </is>
       </c>
       <c r="C782" s="12" t="inlineStr"/>
@@ -13236,12 +13232,12 @@
     <row r="783" ht="25" customHeight="1">
       <c r="A783" s="12" t="inlineStr">
         <is>
-          <t>✏ Работа и услуги в Нетания ⒿⓄⒷ</t>
+          <t>Хайфа и крает,все что приносит деньги, купля, продажа.</t>
         </is>
       </c>
       <c r="B783" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/JobNetaniyaRus</t>
+          <t>https://www.facebook.com/groups/1727807490815553</t>
         </is>
       </c>
       <c r="C783" s="12" t="inlineStr"/>
@@ -13249,12 +13245,12 @@
     <row r="784" ht="25" customHeight="1">
       <c r="A784" s="12" t="inlineStr">
         <is>
-          <t>Хайфа и крает,все что приносит деньги, купля, продажа.</t>
+          <t>Девушки в Ашкелоне. Израиль</t>
         </is>
       </c>
       <c r="B784" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1727807490815553</t>
+          <t>https://www.facebook.com/groups/1487164511840096</t>
         </is>
       </c>
       <c r="C784" s="12" t="inlineStr"/>
@@ -13262,12 +13258,12 @@
     <row r="785" ht="25" customHeight="1">
       <c r="A785" s="12" t="inlineStr">
         <is>
-          <t>Девушки в Ашкелоне. Израиль</t>
+          <t>ИЗРАИЛЬ, 90-е. КАК ЭТО БЫЛО</t>
         </is>
       </c>
       <c r="B785" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1487164511840096</t>
+          <t>https://www.facebook.com/groups/2136937326765996</t>
         </is>
       </c>
       <c r="C785" s="12" t="inlineStr"/>
@@ -13275,12 +13271,12 @@
     <row r="786" ht="25" customHeight="1">
       <c r="A786" s="12" t="inlineStr">
         <is>
-          <t>ИЗРАИЛЬ, 90-е. КАК ЭТО БЫЛО</t>
+          <t>Отдам даром Хайфа и Крайот</t>
         </is>
       </c>
       <c r="B786" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/2136937326765996</t>
+          <t>https://www.facebook.com/groups/870940640782147</t>
         </is>
       </c>
       <c r="C786" s="12" t="inlineStr"/>
@@ -13288,12 +13284,12 @@
     <row r="787" ht="25" customHeight="1">
       <c r="A787" s="12" t="inlineStr">
         <is>
-          <t>Отдам даром Хайфа и Крайот</t>
+          <t>Беэр-Шева,Негев и весь Израиль.</t>
         </is>
       </c>
       <c r="B787" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/870940640782147</t>
+          <t>https://www.facebook.com/groups/2340185702926960</t>
         </is>
       </c>
       <c r="C787" s="12" t="inlineStr"/>
@@ -13301,12 +13297,12 @@
     <row r="788" ht="25" customHeight="1">
       <c r="A788" s="12" t="inlineStr">
         <is>
-          <t>Беэр-Шева,Негев и весь Израиль.</t>
+          <t>Беэр Шева работа - Работа в Беэр Шеве - Беер Шева</t>
         </is>
       </c>
       <c r="B788" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/2340185702926960</t>
+          <t>https://www.facebook.com/groups/rabotabeersheva</t>
         </is>
       </c>
       <c r="C788" s="12" t="inlineStr"/>
@@ -13314,12 +13310,12 @@
     <row r="789" ht="25" customHeight="1">
       <c r="A789" s="12" t="inlineStr">
         <is>
-          <t>Беэр Шева работа - Работа в Беэр Шеве - Беер Шева</t>
+          <t>Квартиры на съем и продажу Нетания _מדליין נכסים למכירה / להשכרה</t>
         </is>
       </c>
       <c r="B789" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/rabotabeersheva</t>
+          <t>https://www.facebook.com/groups/1024081791258176</t>
         </is>
       </c>
       <c r="C789" s="12" t="inlineStr"/>
@@ -13327,55 +13323,55 @@
     <row r="790" ht="25" customHeight="1">
       <c r="A790" s="12" t="inlineStr">
         <is>
-          <t>Квартиры на съем и продажу Нетания _מדליין נכסים למכירה / להשכרה</t>
+          <t>Снять, продать Ашдод квартиры.</t>
         </is>
       </c>
       <c r="B790" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1024081791258176</t>
+          <t>https://www.facebook.com/groups/774309706646373</t>
         </is>
       </c>
       <c r="C790" s="12" t="inlineStr"/>
     </row>
     <row r="791" ht="25" customHeight="1">
-      <c r="A791" s="12" t="inlineStr">
-        <is>
-          <t>Снять, продать Ашдод квартиры.</t>
-        </is>
-      </c>
-      <c r="B791" s="12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/774309706646373</t>
-        </is>
-      </c>
-      <c r="C791" s="12" t="inlineStr"/>
+      <c r="A791" s="18" t="inlineStr">
+        <is>
+          <t>БАРСКИЕ ЗАМАШКИ</t>
+        </is>
+      </c>
+      <c r="B791" s="18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/211400102345889</t>
+        </is>
+      </c>
+      <c r="C791" s="18" t="inlineStr">
+        <is>
+          <t>Error_NoPostField</t>
+        </is>
+      </c>
     </row>
     <row r="792" ht="25" customHeight="1">
-      <c r="A792" s="18" t="inlineStr">
-        <is>
-          <t>БАРСКИЕ ЗАМАШКИ</t>
-        </is>
-      </c>
-      <c r="B792" s="18" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/211400102345889</t>
-        </is>
-      </c>
-      <c r="C792" s="18" t="inlineStr">
-        <is>
-          <t>Error_NoPostField</t>
-        </is>
-      </c>
+      <c r="A792" s="12" t="inlineStr">
+        <is>
+          <t>Работа в Реховоте</t>
+        </is>
+      </c>
+      <c r="B792" s="12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/759252605833929</t>
+        </is>
+      </c>
+      <c r="C792" s="12" t="inlineStr"/>
     </row>
     <row r="793" ht="25" customHeight="1">
       <c r="A793" s="12" t="inlineStr">
         <is>
-          <t>Работа в Реховоте</t>
+          <t>Нетания - Квартиры на Сьем/Продажу</t>
         </is>
       </c>
       <c r="B793" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/759252605833929</t>
+          <t>https://www.facebook.com/groups/680206919435357</t>
         </is>
       </c>
       <c r="C793" s="12" t="inlineStr"/>
@@ -13383,12 +13379,12 @@
     <row r="794" ht="25" customHeight="1">
       <c r="A794" s="12" t="inlineStr">
         <is>
-          <t>Нетания - Квартиры на Сьем/Продажу</t>
+          <t>НЕТАНИЯ - ТОЛЬКО квартиры на съем | שכירויות בלבד</t>
         </is>
       </c>
       <c r="B794" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/680206919435357</t>
+          <t>https://www.facebook.com/groups/rentinnetanya</t>
         </is>
       </c>
       <c r="C794" s="12" t="inlineStr"/>
@@ -13396,59 +13392,59 @@
     <row r="795" ht="25" customHeight="1">
       <c r="A795" s="12" t="inlineStr">
         <is>
-          <t>НЕТАНИЯ - ТОЛЬКО квартиры на съем | שכירויות בלבד</t>
+          <t>Ирландия Жилье Квартиры Дома Аренда Сеть Помогаем Нашим!</t>
         </is>
       </c>
       <c r="B795" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/rentinnetanya</t>
-        </is>
-      </c>
-      <c r="C795" s="12" t="inlineStr"/>
+          <t>https://www.facebook.com/groups/pn.ireland.housing</t>
+        </is>
+      </c>
+      <c r="C795" s="12" t="inlineStr">
+        <is>
+          <t>Ирландия</t>
+        </is>
+      </c>
     </row>
     <row r="796" ht="25" customHeight="1">
-      <c r="A796" s="12" t="inlineStr">
-        <is>
-          <t>Ирландия Жилье Квартиры Дома Аренда Сеть Помогаем Нашим!</t>
-        </is>
-      </c>
-      <c r="B796" s="12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/pn.ireland.housing</t>
-        </is>
-      </c>
-      <c r="C796" s="12" t="inlineStr">
-        <is>
-          <t>Ирландия</t>
+      <c r="A796" s="18" t="inlineStr">
+        <is>
+          <t>Работа в Натании</t>
+        </is>
+      </c>
+      <c r="B796" s="18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/873298086383121</t>
+        </is>
+      </c>
+      <c r="C796" s="18" t="inlineStr">
+        <is>
+          <t>Error_NoPostField</t>
         </is>
       </c>
     </row>
     <row r="797" ht="25" customHeight="1">
-      <c r="A797" s="18" t="inlineStr">
-        <is>
-          <t>Работа в Натании</t>
-        </is>
-      </c>
-      <c r="B797" s="18" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/873298086383121</t>
-        </is>
-      </c>
-      <c r="C797" s="18" t="inlineStr">
-        <is>
-          <t>Error_NoPostField</t>
-        </is>
-      </c>
+      <c r="A797" s="12" t="inlineStr">
+        <is>
+          <t>Работа в нетании -хадере</t>
+        </is>
+      </c>
+      <c r="B797" s="12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1900933010171761</t>
+        </is>
+      </c>
+      <c r="C797" s="12" t="inlineStr"/>
     </row>
     <row r="798" ht="25" customHeight="1">
       <c r="A798" s="12" t="inlineStr">
         <is>
-          <t>Работа в нетании -хадере</t>
+          <t>Работа в Израиле/עבודה בכל הארץ ובכל התחומים</t>
         </is>
       </c>
       <c r="B798" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1900933010171761</t>
+          <t>https://www.facebook.com/groups/413264492216080</t>
         </is>
       </c>
       <c r="C798" s="12" t="inlineStr"/>
@@ -13456,12 +13452,12 @@
     <row r="799" ht="25" customHeight="1">
       <c r="A799" s="12" t="inlineStr">
         <is>
-          <t>Работа в Израиле/עבודה בכל הארץ ובכל התחומים</t>
+          <t>Работа в Израиле</t>
         </is>
       </c>
       <c r="B799" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/413264492216080</t>
+          <t>https://www.facebook.com/groups/292945147812027</t>
         </is>
       </c>
       <c r="C799" s="12" t="inlineStr"/>
@@ -13469,12 +13465,12 @@
     <row r="800" ht="25" customHeight="1">
       <c r="A800" s="12" t="inlineStr">
         <is>
-          <t>Работа в Израиле</t>
+          <t>Работаем в Израиле!</t>
         </is>
       </c>
       <c r="B800" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/292945147812027</t>
+          <t>https://www.facebook.com/groups/1274597352880777</t>
         </is>
       </c>
       <c r="C800" s="12" t="inlineStr"/>
@@ -13482,12 +13478,12 @@
     <row r="801" ht="25" customHeight="1">
       <c r="A801" s="12" t="inlineStr">
         <is>
-          <t>Работаем в Израиле!</t>
+          <t>Доска бесплатных  объявлений Израиля.</t>
         </is>
       </c>
       <c r="B801" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1274597352880777</t>
+          <t>https://www.facebook.com/groups/1447797655538261</t>
         </is>
       </c>
       <c r="C801" s="12" t="inlineStr"/>
@@ -13495,12 +13491,12 @@
     <row r="802" ht="25" customHeight="1">
       <c r="A802" s="12" t="inlineStr">
         <is>
-          <t>Доска бесплатных  объявлений Израиля.</t>
+          <t>Работа в Израиле. Реальные бесплатные и платные вакансии.</t>
         </is>
       </c>
       <c r="B802" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1447797655538261</t>
+          <t>https://www.facebook.com/groups/1267853343300180</t>
         </is>
       </c>
       <c r="C802" s="12" t="inlineStr"/>
@@ -13508,12 +13504,12 @@
     <row r="803" ht="25" customHeight="1">
       <c r="A803" s="12" t="inlineStr">
         <is>
-          <t>Работа в Израиле. Реальные бесплатные и платные вакансии.</t>
+          <t>Работа и вакансии на юге и в центре Израиля.</t>
         </is>
       </c>
       <c r="B803" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1267853343300180</t>
+          <t>https://www.facebook.com/groups/1613712888943873</t>
         </is>
       </c>
       <c r="C803" s="12" t="inlineStr"/>
@@ -13521,59 +13517,59 @@
     <row r="804" ht="25" customHeight="1">
       <c r="A804" s="12" t="inlineStr">
         <is>
-          <t>Работа и вакансии на юге и в центре Израиля.</t>
+          <t>НИДЕРЛАНДЫ Амстердам Роттердам Гаага Утрехт Эйндховен Тилбург Алмере ...</t>
         </is>
       </c>
       <c r="B804" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1613712888943873</t>
-        </is>
-      </c>
-      <c r="C804" s="12" t="inlineStr"/>
+          <t>https://www.facebook.com/groups/netherlandschat</t>
+        </is>
+      </c>
+      <c r="C804" s="12" t="inlineStr">
+        <is>
+          <t>Роттердам</t>
+        </is>
+      </c>
     </row>
     <row r="805" ht="25" customHeight="1">
-      <c r="A805" s="12" t="inlineStr">
-        <is>
-          <t>НИДЕРЛАНДЫ Амстердам Роттердам Гаага Утрехт Эйндховен Тилбург Алмере ...</t>
-        </is>
-      </c>
-      <c r="B805" s="12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/netherlandschat</t>
-        </is>
-      </c>
-      <c r="C805" s="12" t="inlineStr">
-        <is>
-          <t>Роттердам</t>
+      <c r="A805" s="18" t="inlineStr">
+        <is>
+          <t>Українці в Нідерландах (Амстердам, Роттердам, Гаага, Утрехт)</t>
+        </is>
+      </c>
+      <c r="B805" s="18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/ukr.in.netherlands</t>
+        </is>
+      </c>
+      <c r="C805" s="18" t="inlineStr">
+        <is>
+          <t>Error_NoPostField</t>
         </is>
       </c>
     </row>
     <row r="806" ht="25" customHeight="1">
-      <c r="A806" s="18" t="inlineStr">
-        <is>
-          <t>Українці в Нідерландах (Амстердам, Роттердам, Гаага, Утрехт)</t>
-        </is>
-      </c>
-      <c r="B806" s="18" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/ukr.in.netherlands</t>
-        </is>
-      </c>
-      <c r="C806" s="18" t="inlineStr">
-        <is>
-          <t>Error_NoPostField</t>
-        </is>
-      </c>
+      <c r="A806" s="12" t="inlineStr">
+        <is>
+          <t>אשקלון וחברים -  Ашкелон и друзья</t>
+        </is>
+      </c>
+      <c r="B806" s="12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/2273787122718533</t>
+        </is>
+      </c>
+      <c r="C806" s="12" t="inlineStr"/>
     </row>
     <row r="807" ht="25" customHeight="1">
       <c r="A807" s="12" t="inlineStr">
         <is>
-          <t>אשקלון וחברים -  Ашкелон и друзья</t>
+          <t>"Наша Галилея" Информация, Новости, Развлечения 24/7 Акко, Нагария, Шломи..</t>
         </is>
       </c>
       <c r="B807" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/2273787122718533</t>
+          <t>https://www.facebook.com/groups/1684976498381216</t>
         </is>
       </c>
       <c r="C807" s="12" t="inlineStr"/>
@@ -13581,12 +13577,12 @@
     <row r="808" ht="25" customHeight="1">
       <c r="A808" s="12" t="inlineStr">
         <is>
-          <t>"Наша Галилея" Информация, Новости, Развлечения 24/7 Акко, Нагария, Шломи..</t>
+          <t>Ришон ле цион реклама</t>
         </is>
       </c>
       <c r="B808" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1684976498381216</t>
+          <t>https://www.facebook.com/groups/1907227079318779</t>
         </is>
       </c>
       <c r="C808" s="12" t="inlineStr"/>
@@ -13594,12 +13590,12 @@
     <row r="809" ht="25" customHeight="1">
       <c r="A809" s="12" t="inlineStr">
         <is>
-          <t>Ришон ле цион реклама</t>
+          <t>Квартиры в Нетании для Репатриантов 2024</t>
         </is>
       </c>
       <c r="B809" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1907227079318779</t>
+          <t>https://www.facebook.com/groups/netanyarent</t>
         </is>
       </c>
       <c r="C809" s="12" t="inlineStr"/>
@@ -13607,12 +13603,12 @@
     <row r="810" ht="25" customHeight="1">
       <c r="A810" s="12" t="inlineStr">
         <is>
-          <t>Квартиры в Нетании для Репатриантов 2024</t>
+          <t>Работа в Нетании עבודה בנתניה</t>
         </is>
       </c>
       <c r="B810" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/netanyarent</t>
+          <t>https://www.facebook.com/groups/615841175595175</t>
         </is>
       </c>
       <c r="C810" s="12" t="inlineStr"/>
@@ -13620,12 +13616,12 @@
     <row r="811" ht="25" customHeight="1">
       <c r="A811" s="12" t="inlineStr">
         <is>
-          <t>Работа в Нетании עבודה בנתניה</t>
+          <t>Реховот /Беэр яков/Ришон -ле-Цион/Нес Циона</t>
         </is>
       </c>
       <c r="B811" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/615841175595175</t>
+          <t>https://www.facebook.com/groups/718458521913045</t>
         </is>
       </c>
       <c r="C811" s="12" t="inlineStr"/>
@@ -13633,76 +13629,80 @@
     <row r="812" ht="25" customHeight="1">
       <c r="A812" s="12" t="inlineStr">
         <is>
-          <t>Реховот /Беэр яков/Ришон -ле-Цион/Нес Циона</t>
+          <t>Русскоговорящие в Голландии</t>
         </is>
       </c>
       <c r="B812" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/718458521913045</t>
-        </is>
-      </c>
-      <c r="C812" s="12" t="inlineStr"/>
+          <t>https://www.facebook.com/groups/1480918645338695</t>
+        </is>
+      </c>
+      <c r="C812" s="12" t="inlineStr">
+        <is>
+          <t>Голландия</t>
+        </is>
+      </c>
     </row>
     <row r="813" ht="25" customHeight="1">
-      <c r="A813" s="12" t="inlineStr">
-        <is>
-          <t>Русскоговорящие в Голландии</t>
-        </is>
-      </c>
-      <c r="B813" s="12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/1480918645338695</t>
-        </is>
-      </c>
-      <c r="C813" s="12" t="inlineStr">
+      <c r="A813" s="11" t="inlineStr">
+        <is>
+          <t>Russen in Nederland; Русские в Голландии!!</t>
+        </is>
+      </c>
+      <c r="B813" s="11" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1193154049028390</t>
+        </is>
+      </c>
+      <c r="C813" s="11" t="inlineStr">
         <is>
           <t>Голландия</t>
         </is>
       </c>
     </row>
     <row r="814" ht="25" customHeight="1">
-      <c r="A814" s="11" t="inlineStr">
-        <is>
-          <t>Russen in Nederland; Русские в Голландии!!</t>
-        </is>
-      </c>
-      <c r="B814" s="11" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/1193154049028390</t>
-        </is>
-      </c>
-      <c r="C814" s="11" t="inlineStr">
-        <is>
-          <t>Голландия</t>
+      <c r="A814" s="12" t="inlineStr">
+        <is>
+          <t>Полезная информация о Ларнаке, Кипр</t>
+        </is>
+      </c>
+      <c r="B814" s="12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/usefulllarnacainformation</t>
+        </is>
+      </c>
+      <c r="C814" s="12" t="inlineStr">
+        <is>
+          <t>Лимасол</t>
         </is>
       </c>
     </row>
     <row r="815" ht="25" customHeight="1">
-      <c r="A815" s="12" t="inlineStr">
-        <is>
-          <t>Полезная информация о Ларнаке, Кипр</t>
-        </is>
-      </c>
-      <c r="B815" s="12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/usefulllarnacainformation</t>
-        </is>
-      </c>
-      <c r="C815" s="12" t="inlineStr">
-        <is>
-          <t>Лимасол</t>
+      <c r="A815" s="18" t="inlineStr">
+        <is>
+          <t>Франция Париж Марсель Ницца Лион Тулуза Бордо Канны Лилль Монпелье</t>
+        </is>
+      </c>
+      <c r="B815" s="18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RussianFranceEU</t>
+        </is>
+      </c>
+      <c r="C815" s="18" t="inlineStr">
+        <is>
+          <t>Error_NoPostField</t>
         </is>
       </c>
     </row>
     <row r="816" ht="25" customHeight="1">
       <c r="A816" s="18" t="inlineStr">
         <is>
-          <t>Франция Париж Марсель Ницца Лион Тулуза Бордо Канны Лилль Монпелье</t>
+          <t>Русскоязычная Франция</t>
         </is>
       </c>
       <c r="B816" s="18" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/RussianFranceEU</t>
+          <t>https://www.facebook.com/groups/509932135787964</t>
         </is>
       </c>
       <c r="C816" s="18" t="inlineStr">
@@ -13712,65 +13712,65 @@
       </c>
     </row>
     <row r="817" ht="25" customHeight="1">
-      <c r="A817" s="18" t="inlineStr">
-        <is>
-          <t>Русскоязычная Франция</t>
-        </is>
-      </c>
-      <c r="B817" s="18" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/509932135787964</t>
-        </is>
-      </c>
-      <c r="C817" s="18" t="inlineStr">
+      <c r="A817" s="12" t="inlineStr">
+        <is>
+          <t>Русскоговорящие во Франции</t>
+        </is>
+      </c>
+      <c r="B817" s="12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/661939260651057</t>
+        </is>
+      </c>
+      <c r="C817" s="12" t="inlineStr">
+        <is>
+          <t>Франция</t>
+        </is>
+      </c>
+    </row>
+    <row r="818" ht="25" customHeight="1">
+      <c r="A818" s="18" t="inlineStr">
+        <is>
+          <t>Красота и здоровье в Париже</t>
+        </is>
+      </c>
+      <c r="B818" s="18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/masajprof</t>
+        </is>
+      </c>
+      <c r="C818" s="18" t="inlineStr">
         <is>
           <t>Error_NoPostField</t>
         </is>
       </c>
     </row>
-    <row r="818" ht="25" customHeight="1">
-      <c r="A818" s="12" t="inlineStr">
-        <is>
-          <t>Русскоговорящие во Франции</t>
-        </is>
-      </c>
-      <c r="B818" s="12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/661939260651057</t>
-        </is>
-      </c>
-      <c r="C818" s="12" t="inlineStr">
-        <is>
-          <t>Франция</t>
-        </is>
-      </c>
-    </row>
     <row r="819" ht="25" customHeight="1">
-      <c r="A819" s="18" t="inlineStr">
-        <is>
-          <t>Красота и здоровье в Париже</t>
-        </is>
-      </c>
-      <c r="B819" s="18" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/masajprof</t>
-        </is>
-      </c>
-      <c r="C819" s="18" t="inlineStr">
-        <is>
-          <t>Error_NoPostField</t>
+      <c r="A819" s="12" t="inlineStr">
+        <is>
+          <t>Париж и IDF Бесплатные объявления/продажа/услуги/аренда/ работа</t>
+        </is>
+      </c>
+      <c r="B819" s="12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/775501567382451</t>
+        </is>
+      </c>
+      <c r="C819" s="12" t="inlineStr">
+        <is>
+          <t>Париж</t>
         </is>
       </c>
     </row>
     <row r="820" ht="25" customHeight="1">
       <c r="A820" s="12" t="inlineStr">
         <is>
-          <t>Париж и IDF Бесплатные объявления/продажа/услуги/аренда/ работа</t>
+          <t>Обьявления в Париже.</t>
         </is>
       </c>
       <c r="B820" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/775501567382451</t>
+          <t>https://www.facebook.com/groups/1803291669817051</t>
         </is>
       </c>
       <c r="C820" s="12" t="inlineStr">
@@ -13782,63 +13782,63 @@
     <row r="821" ht="25" customHeight="1">
       <c r="A821" s="12" t="inlineStr">
         <is>
-          <t>Обьявления в Париже.</t>
+          <t>ОБЪЯВЛЕНИЯ ФРАНЦИЯ 🇪🇺❤️ Услуги/ Работа</t>
         </is>
       </c>
       <c r="B821" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1803291669817051</t>
+          <t>https://www.facebook.com/groups/1183227449211802</t>
         </is>
       </c>
       <c r="C821" s="12" t="inlineStr">
         <is>
+          <t>Франция</t>
+        </is>
+      </c>
+    </row>
+    <row r="822" ht="25" customHeight="1">
+      <c r="A822" s="18" t="inlineStr">
+        <is>
+          <t>Париж Услуги Paris Services Network Помогаем Нашим!</t>
+        </is>
+      </c>
+      <c r="B822" s="18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/pn.france.srv</t>
+        </is>
+      </c>
+      <c r="C822" s="18" t="inlineStr">
+        <is>
+          <t>Error_NoPostField</t>
+        </is>
+      </c>
+    </row>
+    <row r="823" ht="25" customHeight="1">
+      <c r="A823" s="12" t="inlineStr">
+        <is>
+          <t>Русскоговорящие в Париже</t>
+        </is>
+      </c>
+      <c r="B823" s="12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/236963333736667</t>
+        </is>
+      </c>
+      <c r="C823" s="12" t="inlineStr">
+        <is>
           <t>Париж</t>
-        </is>
-      </c>
-    </row>
-    <row r="822" ht="25" customHeight="1">
-      <c r="A822" s="12" t="inlineStr">
-        <is>
-          <t>ОБЪЯВЛЕНИЯ ФРАНЦИЯ 🇪🇺❤️ Услуги/ Работа</t>
-        </is>
-      </c>
-      <c r="B822" s="12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/1183227449211802</t>
-        </is>
-      </c>
-      <c r="C822" s="12" t="inlineStr">
-        <is>
-          <t>Франция</t>
-        </is>
-      </c>
-    </row>
-    <row r="823" ht="25" customHeight="1">
-      <c r="A823" s="18" t="inlineStr">
-        <is>
-          <t>Париж Услуги Paris Services Network Помогаем Нашим!</t>
-        </is>
-      </c>
-      <c r="B823" s="18" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/pn.france.srv</t>
-        </is>
-      </c>
-      <c r="C823" s="18" t="inlineStr">
-        <is>
-          <t>Error_NoPostField</t>
         </is>
       </c>
     </row>
     <row r="824" ht="25" customHeight="1">
       <c r="A824" s="12" t="inlineStr">
         <is>
-          <t>Русскоговорящие в Париже</t>
+          <t>В ПАРИЖЕ ТОЛЬКО ДЕВУШКИ</t>
         </is>
       </c>
       <c r="B824" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/236963333736667</t>
+          <t>https://www.facebook.com/groups/463722857154541</t>
         </is>
       </c>
       <c r="C824" s="12" t="inlineStr">
@@ -13850,12 +13850,12 @@
     <row r="825" ht="25" customHeight="1">
       <c r="A825" s="12" t="inlineStr">
         <is>
-          <t>В ПАРИЖЕ ТОЛЬКО ДЕВУШКИ</t>
+          <t>Париж</t>
         </is>
       </c>
       <c r="B825" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/463722857154541</t>
+          <t>https://www.facebook.com/groups/739330472938335</t>
         </is>
       </c>
       <c r="C825" s="12" t="inlineStr">
@@ -13872,7 +13872,7 @@
       </c>
       <c r="B826" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/739330472938335</t>
+          <t>https://www.facebook.com/groups/876881192365466</t>
         </is>
       </c>
       <c r="C826" s="12" t="inlineStr">
@@ -13884,12 +13884,12 @@
     <row r="827" ht="25" customHeight="1">
       <c r="A827" s="12" t="inlineStr">
         <is>
-          <t>Париж</t>
+          <t>Париж каждый день ФРАНЦИЯ🌎</t>
         </is>
       </c>
       <c r="B827" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/876881192365466</t>
+          <t>https://www.facebook.com/groups/862857244942429</t>
         </is>
       </c>
       <c r="C827" s="12" t="inlineStr">
@@ -13901,12 +13901,12 @@
     <row r="828" ht="25" customHeight="1">
       <c r="A828" s="12" t="inlineStr">
         <is>
-          <t>Париж каждый день ФРАНЦИЯ🌎</t>
+          <t>Русскоговорящий Париж</t>
         </is>
       </c>
       <c r="B828" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/862857244942429</t>
+          <t>https://www.facebook.com/groups/1433593677516464</t>
         </is>
       </c>
       <c r="C828" s="12" t="inlineStr">
@@ -13918,12 +13918,12 @@
     <row r="829" ht="25" customHeight="1">
       <c r="A829" s="12" t="inlineStr">
         <is>
-          <t>Русскоговорящий Париж</t>
+          <t>Окно в Париж</t>
         </is>
       </c>
       <c r="B829" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1433593677516464</t>
+          <t>https://www.facebook.com/groups/oknovparis.fr</t>
         </is>
       </c>
       <c r="C829" s="12" t="inlineStr">
@@ -13935,12 +13935,12 @@
     <row r="830" ht="25" customHeight="1">
       <c r="A830" s="12" t="inlineStr">
         <is>
-          <t>Окно в Париж</t>
+          <t>Доска объявлений париж</t>
         </is>
       </c>
       <c r="B830" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/oknovparis.fr</t>
+          <t>https://www.facebook.com/groups/francerustur</t>
         </is>
       </c>
       <c r="C830" s="12" t="inlineStr">
@@ -13952,12 +13952,12 @@
     <row r="831" ht="25" customHeight="1">
       <c r="A831" s="12" t="inlineStr">
         <is>
-          <t>Доска объявлений париж</t>
+          <t>ПРИВЕТ ПАРИЖ / SALUT PARIS / HELLO PARIS</t>
         </is>
       </c>
       <c r="B831" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/francerustur</t>
+          <t>https://www.facebook.com/groups/154348015314678</t>
         </is>
       </c>
       <c r="C831" s="12" t="inlineStr">
@@ -13969,12 +13969,12 @@
     <row r="832" ht="25" customHeight="1">
       <c r="A832" s="12" t="inlineStr">
         <is>
-          <t>ПРИВЕТ ПАРИЖ / SALUT PARIS / HELLO PARIS</t>
+          <t>БЕСПЛАТНЫЕ ОБЪЯВЛЕНИЯ Франция Париж Марсель Лион Тулуза Ницца Нант Бордо</t>
         </is>
       </c>
       <c r="B832" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/154348015314678</t>
+          <t>https://www.facebook.com/groups/1685417268292577</t>
         </is>
       </c>
       <c r="C832" s="12" t="inlineStr">
@@ -13986,12 +13986,12 @@
     <row r="833" ht="25" customHeight="1">
       <c r="A833" s="12" t="inlineStr">
         <is>
-          <t>БЕСПЛАТНЫЕ ОБЪЯВЛЕНИЯ Франция Париж Марсель Лион Тулуза Ницца Нант Бордо</t>
+          <t>Наш Париж 🇫🇷</t>
         </is>
       </c>
       <c r="B833" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1685417268292577</t>
+          <t>https://www.facebook.com/groups/3480079572258689</t>
         </is>
       </c>
       <c r="C833" s="12" t="inlineStr">
@@ -14003,12 +14003,12 @@
     <row r="834" ht="25" customHeight="1">
       <c r="A834" s="12" t="inlineStr">
         <is>
-          <t>Наш Париж 🇫🇷</t>
+          <t>Русскоязычные в Париже🇫🇷</t>
         </is>
       </c>
       <c r="B834" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/3480079572258689</t>
+          <t>https://www.facebook.com/groups/1975913022697907</t>
         </is>
       </c>
       <c r="C834" s="12" t="inlineStr">
@@ -14020,12 +14020,12 @@
     <row r="835" ht="25" customHeight="1">
       <c r="A835" s="12" t="inlineStr">
         <is>
-          <t>Русскоязычные в Париже🇫🇷</t>
+          <t>Париж, Франция (Paris, France)</t>
         </is>
       </c>
       <c r="B835" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1975913022697907</t>
+          <t>https://www.facebook.com/groups/parischat</t>
         </is>
       </c>
       <c r="C835" s="12" t="inlineStr">
@@ -14035,48 +14035,48 @@
       </c>
     </row>
     <row r="836" ht="25" customHeight="1">
-      <c r="A836" s="12" t="inlineStr">
-        <is>
-          <t>Париж, Франция (Paris, France)</t>
-        </is>
-      </c>
-      <c r="B836" s="12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/parischat</t>
-        </is>
-      </c>
-      <c r="C836" s="12" t="inlineStr">
+      <c r="A836" s="18" t="inlineStr">
+        <is>
+          <t>Русскоязычные в Париж€</t>
+        </is>
+      </c>
+      <c r="B836" s="18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1539217322880764</t>
+        </is>
+      </c>
+      <c r="C836" s="18" t="inlineStr">
+        <is>
+          <t>Error_NoPostField</t>
+        </is>
+      </c>
+    </row>
+    <row r="837" ht="25" customHeight="1">
+      <c r="A837" s="12" t="inlineStr">
+        <is>
+          <t>✔️РУССКИЕ В ПАРИЖЕ 🇫🇷 Paris, Париж</t>
+        </is>
+      </c>
+      <c r="B837" s="12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/russianpeople.paris</t>
+        </is>
+      </c>
+      <c r="C837" s="12" t="inlineStr">
         <is>
           <t>Париж</t>
-        </is>
-      </c>
-    </row>
-    <row r="837" ht="25" customHeight="1">
-      <c r="A837" s="18" t="inlineStr">
-        <is>
-          <t>Русскоязычные в Париж€</t>
-        </is>
-      </c>
-      <c r="B837" s="18" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/1539217322880764</t>
-        </is>
-      </c>
-      <c r="C837" s="18" t="inlineStr">
-        <is>
-          <t>Error_NoPostField</t>
         </is>
       </c>
     </row>
     <row r="838" ht="25" customHeight="1">
       <c r="A838" s="12" t="inlineStr">
         <is>
-          <t>✔️РУССКИЕ В ПАРИЖЕ 🇫🇷 Paris, Париж</t>
+          <t>Бесплатный париж</t>
         </is>
       </c>
       <c r="B838" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/russianpeople.paris</t>
+          <t>https://www.facebook.com/groups/1725248144372514</t>
         </is>
       </c>
       <c r="C838" s="12" t="inlineStr">
@@ -14088,12 +14088,12 @@
     <row r="839" ht="25" customHeight="1">
       <c r="A839" s="12" t="inlineStr">
         <is>
-          <t>Бесплатный париж</t>
+          <t>Русские в Париже</t>
         </is>
       </c>
       <c r="B839" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1725248144372514</t>
+          <t>https://www.facebook.com/groups/1446680535625652</t>
         </is>
       </c>
       <c r="C839" s="12" t="inlineStr">
@@ -14105,12 +14105,12 @@
     <row r="840" ht="25" customHeight="1">
       <c r="A840" s="12" t="inlineStr">
         <is>
-          <t>Русские в Париже</t>
+          <t>Париж Услуги</t>
         </is>
       </c>
       <c r="B840" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1446680535625652</t>
+          <t>https://www.facebook.com/groups/1624990704491581</t>
         </is>
       </c>
       <c r="C840" s="12" t="inlineStr">
@@ -14122,12 +14122,12 @@
     <row r="841" ht="25" customHeight="1">
       <c r="A841" s="12" t="inlineStr">
         <is>
-          <t>Париж Услуги</t>
+          <t>САРАФАННОЕ РАДИО ПАРИЖА</t>
         </is>
       </c>
       <c r="B841" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1624990704491581</t>
+          <t>https://www.facebook.com/groups/331689760374135</t>
         </is>
       </c>
       <c r="C841" s="12" t="inlineStr">
@@ -14139,12 +14139,12 @@
     <row r="842" ht="25" customHeight="1">
       <c r="A842" s="12" t="inlineStr">
         <is>
-          <t>САРАФАННОЕ РАДИО ПАРИЖА</t>
+          <t>ПАРИЖ ❤️ ФРАНЦИЯ</t>
         </is>
       </c>
       <c r="B842" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/331689760374135</t>
+          <t>https://www.facebook.com/groups/francefrancefrance</t>
         </is>
       </c>
       <c r="C842" s="12" t="inlineStr">
@@ -14156,12 +14156,12 @@
     <row r="843" ht="25" customHeight="1">
       <c r="A843" s="12" t="inlineStr">
         <is>
-          <t>ПАРИЖ ❤️ ФРАНЦИЯ</t>
+          <t>Деловой Париж</t>
         </is>
       </c>
       <c r="B843" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/francefrancefrance</t>
+          <t>https://www.facebook.com/groups/185586221485367</t>
         </is>
       </c>
       <c r="C843" s="12" t="inlineStr">
@@ -14173,46 +14173,46 @@
     <row r="844" ht="25" customHeight="1">
       <c r="A844" s="12" t="inlineStr">
         <is>
-          <t>Деловой Париж</t>
+          <t>Русскоязычная Франция</t>
         </is>
       </c>
       <c r="B844" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/185586221485367</t>
+          <t>https://www.facebook.com/groups/642325713144676</t>
         </is>
       </c>
       <c r="C844" s="12" t="inlineStr">
         <is>
-          <t>Париж</t>
+          <t>Франция</t>
         </is>
       </c>
     </row>
     <row r="845" ht="25" customHeight="1">
       <c r="A845" s="12" t="inlineStr">
         <is>
-          <t>Русскоязычная Франция</t>
+          <t>Русскоговорящие в Париже</t>
         </is>
       </c>
       <c r="B845" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/642325713144676</t>
+          <t>https://www.facebook.com/groups/russophones.paris</t>
         </is>
       </c>
       <c r="C845" s="12" t="inlineStr">
         <is>
-          <t>Франция</t>
+          <t>Париж</t>
         </is>
       </c>
     </row>
     <row r="846" ht="25" customHeight="1">
       <c r="A846" s="12" t="inlineStr">
         <is>
-          <t>Русскоговорящие в Париже</t>
+          <t>Русскоязычный Париж</t>
         </is>
       </c>
       <c r="B846" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/russophones.paris</t>
+          <t>https://www.facebook.com/groups/2212944515661736</t>
         </is>
       </c>
       <c r="C846" s="12" t="inlineStr">
@@ -14224,29 +14224,29 @@
     <row r="847" ht="25" customHeight="1">
       <c r="A847" s="12" t="inlineStr">
         <is>
-          <t>Русскоязычный Париж</t>
+          <t>✔ ДЕВОЧКИ И МАЛЬЧИКИ БАРСЕЛОНЫ И ЕЁ ПРИГОРОДОВ/ Barcelona Барселона✔</t>
         </is>
       </c>
       <c r="B847" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/2212944515661736</t>
+          <t>https://www.facebook.com/groups/devochki.barcelona</t>
         </is>
       </c>
       <c r="C847" s="12" t="inlineStr">
         <is>
-          <t>Париж</t>
+          <t>Барселона</t>
         </is>
       </c>
     </row>
     <row r="848" ht="25" customHeight="1">
       <c r="A848" s="12" t="inlineStr">
         <is>
-          <t>✔ ДЕВОЧКИ И МАЛЬЧИКИ БАРСЕЛОНЫ И ЕЁ ПРИГОРОДОВ/ Barcelona Барселона✔</t>
+          <t>Объявления Barcelona �</t>
         </is>
       </c>
       <c r="B848" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/devochki.barcelona</t>
+          <t>https://www.facebook.com/groups/823607145558796</t>
         </is>
       </c>
       <c r="C848" s="12" t="inlineStr">
@@ -14256,48 +14256,48 @@
       </c>
     </row>
     <row r="849" ht="25" customHeight="1">
-      <c r="A849" s="12" t="inlineStr">
-        <is>
-          <t>Объявления Barcelona �</t>
-        </is>
-      </c>
-      <c r="B849" s="12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/823607145558796</t>
-        </is>
-      </c>
-      <c r="C849" s="12" t="inlineStr">
+      <c r="A849" s="18" t="inlineStr">
+        <is>
+          <t>Девочки Барселоны и окрестностей ( Baix Llobregat )</t>
+        </is>
+      </c>
+      <c r="B849" s="18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/2318381971570321</t>
+        </is>
+      </c>
+      <c r="C849" s="18" t="inlineStr">
+        <is>
+          <t>Error_NoPostField</t>
+        </is>
+      </c>
+    </row>
+    <row r="850" ht="25" customHeight="1">
+      <c r="A850" s="12" t="inlineStr">
+        <is>
+          <t>Доска обьявлений☆Барселона(Испания)</t>
+        </is>
+      </c>
+      <c r="B850" s="12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/tablonspain</t>
+        </is>
+      </c>
+      <c r="C850" s="12" t="inlineStr">
         <is>
           <t>Барселона</t>
-        </is>
-      </c>
-    </row>
-    <row r="850" ht="25" customHeight="1">
-      <c r="A850" s="18" t="inlineStr">
-        <is>
-          <t>Девочки Барселоны и окрестностей ( Baix Llobregat )</t>
-        </is>
-      </c>
-      <c r="B850" s="18" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/2318381971570321</t>
-        </is>
-      </c>
-      <c r="C850" s="18" t="inlineStr">
-        <is>
-          <t>Error_NoPostField</t>
         </is>
       </c>
     </row>
     <row r="851" ht="25" customHeight="1">
       <c r="A851" s="12" t="inlineStr">
         <is>
-          <t>Доска обьявлений☆Барселона(Испания)</t>
+          <t>Наша Барселона</t>
         </is>
       </c>
       <c r="B851" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/tablonspain</t>
+          <t>https://www.facebook.com/groups/994887334239063</t>
         </is>
       </c>
       <c r="C851" s="12" t="inlineStr">
@@ -14309,12 +14309,12 @@
     <row r="852" ht="25" customHeight="1">
       <c r="A852" s="12" t="inlineStr">
         <is>
-          <t>Наша Барселона</t>
+          <t>⭐️БАРСЕЛОНА ВСЁ ВСЁ⭐️</t>
         </is>
       </c>
       <c r="B852" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/994887334239063</t>
+          <t>https://www.facebook.com/groups/490451001765643</t>
         </is>
       </c>
       <c r="C852" s="12" t="inlineStr">
@@ -14326,12 +14326,12 @@
     <row r="853" ht="25" customHeight="1">
       <c r="A853" s="12" t="inlineStr">
         <is>
-          <t>⭐️БАРСЕЛОНА ВСЁ ВСЁ⭐️</t>
+          <t>Испания | Каталония | Барселона | побережье Maresme</t>
         </is>
       </c>
       <c r="B853" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/490451001765643</t>
+          <t>https://www.facebook.com/groups/barcelonamaresme</t>
         </is>
       </c>
       <c r="C853" s="12" t="inlineStr">
@@ -14343,12 +14343,12 @@
     <row r="854" ht="25" customHeight="1">
       <c r="A854" s="12" t="inlineStr">
         <is>
-          <t>Испания | Каталония | Барселона | побережье Maresme</t>
+          <t>БАРСЕЛОНА</t>
         </is>
       </c>
       <c r="B854" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/barcelonamaresme</t>
+          <t>https://www.facebook.com/groups/537635061803129</t>
         </is>
       </c>
       <c r="C854" s="12" t="inlineStr">
@@ -14360,12 +14360,12 @@
     <row r="855" ht="25" customHeight="1">
       <c r="A855" s="12" t="inlineStr">
         <is>
-          <t>БАРСЕЛОНА</t>
+          <t>🇪🇦 БАРСЕЛОНА BARCELONA 🇪🇦 РУССКОГОВОРЯЩИЕ РЕКЛАМА НОВОСТИ РАБОТА УСЛУГИ</t>
         </is>
       </c>
       <c r="B855" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/537635061803129</t>
+          <t>https://www.facebook.com/groups/498908665841795</t>
         </is>
       </c>
       <c r="C855" s="12" t="inlineStr">
@@ -14377,12 +14377,12 @@
     <row r="856" ht="25" customHeight="1">
       <c r="A856" s="12" t="inlineStr">
         <is>
-          <t>🇪🇦 БАРСЕЛОНА BARCELONA 🇪🇦 РУССКОГОВОРЯЩИЕ РЕКЛАМА НОВОСТИ РАБОТА УСЛУГИ</t>
+          <t>Доска объявлений Барселона - Испания</t>
         </is>
       </c>
       <c r="B856" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/498908665841795</t>
+          <t>https://www.facebook.com/groups/299822767153262</t>
         </is>
       </c>
       <c r="C856" s="12" t="inlineStr">
@@ -14394,12 +14394,12 @@
     <row r="857" ht="25" customHeight="1">
       <c r="A857" s="12" t="inlineStr">
         <is>
-          <t>Доска объявлений Барселона - Испания</t>
+          <t>Барселона Объявления</t>
         </is>
       </c>
       <c r="B857" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/299822767153262</t>
+          <t>https://www.facebook.com/groups/adsbarcelona</t>
         </is>
       </c>
       <c r="C857" s="12" t="inlineStr">
@@ -14411,12 +14411,12 @@
     <row r="858" ht="25" customHeight="1">
       <c r="A858" s="12" t="inlineStr">
         <is>
-          <t>Барселона Объявления</t>
+          <t>Девочки Барселоны. И мальчики тоже. А также всего испанского королевства.</t>
         </is>
       </c>
       <c r="B858" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/adsbarcelona</t>
+          <t>https://www.facebook.com/groups/1118265978598073</t>
         </is>
       </c>
       <c r="C858" s="12" t="inlineStr">
@@ -14428,12 +14428,12 @@
     <row r="859" ht="25" customHeight="1">
       <c r="A859" s="12" t="inlineStr">
         <is>
-          <t>Девочки Барселоны. И мальчики тоже. А также всего испанского королевства.</t>
+          <t>ANUNCIOS BARCELONA / ОБЪЯВЛЕНИЯ БАРСЕЛОНА</t>
         </is>
       </c>
       <c r="B859" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1118265978598073</t>
+          <t>https://www.facebook.com/groups/930715078985548</t>
         </is>
       </c>
       <c r="C859" s="12" t="inlineStr">
@@ -14445,29 +14445,29 @@
     <row r="860" ht="25" customHeight="1">
       <c r="A860" s="12" t="inlineStr">
         <is>
-          <t>ANUNCIOS BARCELONA / ОБЪЯВЛЕНИЯ БАРСЕЛОНА</t>
+          <t>Русские в Барселоне</t>
         </is>
       </c>
       <c r="B860" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/930715078985548</t>
+          <t>https://www.facebook.com/groups/271858111494847</t>
         </is>
       </c>
       <c r="C860" s="12" t="inlineStr">
         <is>
-          <t>Барселона</t>
+          <t>Error_NoPostField</t>
         </is>
       </c>
     </row>
     <row r="861" ht="25" customHeight="1">
       <c r="A861" s="12" t="inlineStr">
         <is>
-          <t>Русские в Барселоне</t>
+          <t>Доска объявлений- Барселона !</t>
         </is>
       </c>
       <c r="B861" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/271858111494847</t>
+          <t>https://www.facebook.com/groups/829147767229340</t>
         </is>
       </c>
       <c r="C861" s="12" t="inlineStr">
@@ -14477,48 +14477,48 @@
       </c>
     </row>
     <row r="862" ht="25" customHeight="1">
-      <c r="A862" s="12" t="inlineStr">
-        <is>
-          <t>Доска объявлений- Барселона !</t>
-        </is>
-      </c>
-      <c r="B862" s="12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/829147767229340</t>
-        </is>
-      </c>
-      <c r="C862" s="12" t="inlineStr">
+      <c r="A862" s="18" t="inlineStr">
+        <is>
+          <t>★ БАРСЕЛОНА - ИНФО ★</t>
+        </is>
+      </c>
+      <c r="B862" s="18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/bcn.info</t>
+        </is>
+      </c>
+      <c r="C862" s="18" t="inlineStr">
+        <is>
+          <t>Error_NoPostField</t>
+        </is>
+      </c>
+    </row>
+    <row r="863" ht="25" customHeight="1">
+      <c r="A863" s="12" t="inlineStr">
+        <is>
+          <t>Услуги Барселона и окрестности</t>
+        </is>
+      </c>
+      <c r="B863" s="12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/187113588466063</t>
+        </is>
+      </c>
+      <c r="C863" s="12" t="inlineStr">
         <is>
           <t>Барселона</t>
-        </is>
-      </c>
-    </row>
-    <row r="863" ht="25" customHeight="1">
-      <c r="A863" s="18" t="inlineStr">
-        <is>
-          <t>★ БАРСЕЛОНА - ИНФО ★</t>
-        </is>
-      </c>
-      <c r="B863" s="18" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/bcn.info</t>
-        </is>
-      </c>
-      <c r="C863" s="18" t="inlineStr">
-        <is>
-          <t>Error_NoPostField</t>
         </is>
       </c>
     </row>
     <row r="864" ht="25" customHeight="1">
       <c r="A864" s="12" t="inlineStr">
         <is>
-          <t>Услуги Барселона и окрестности</t>
+          <t>Русскоязычная Барселона и пригороды</t>
         </is>
       </c>
       <c r="B864" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/187113588466063</t>
+          <t>https://www.facebook.com/groups/270875648301520</t>
         </is>
       </c>
       <c r="C864" s="12" t="inlineStr">
@@ -14530,29 +14530,29 @@
     <row r="865" ht="25" customHeight="1">
       <c r="A865" s="12" t="inlineStr">
         <is>
-          <t>Русскоязычная Барселона и пригороды</t>
+          <t>Ищу в Аликанте</t>
         </is>
       </c>
       <c r="B865" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/270875648301520</t>
+          <t>https://www.facebook.com/groups/472912163614645</t>
         </is>
       </c>
       <c r="C865" s="12" t="inlineStr">
         <is>
-          <t>Барселона</t>
+          <t>Аликанте</t>
         </is>
       </c>
     </row>
     <row r="866" ht="25" customHeight="1">
       <c r="A866" s="12" t="inlineStr">
         <is>
-          <t>Ищу в Аликанте</t>
+          <t>Аликанте и окрестности COSTA BLANCA (Всё для всех Всё в одном)</t>
         </is>
       </c>
       <c r="B866" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/472912163614645</t>
+          <t>https://www.facebook.com/groups/340147616867001</t>
         </is>
       </c>
       <c r="C866" s="12" t="inlineStr">
@@ -14562,48 +14562,48 @@
       </c>
     </row>
     <row r="867" ht="25" customHeight="1">
-      <c r="A867" s="12" t="inlineStr">
-        <is>
-          <t>Аликанте и окрестности COSTA BLANCA (Всё для всех Всё в одном)</t>
-        </is>
-      </c>
-      <c r="B867" s="12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/340147616867001</t>
-        </is>
-      </c>
-      <c r="C867" s="12" t="inlineStr">
+      <c r="A867" s="18" t="inlineStr">
+        <is>
+          <t>ДЕВОЧКИ ИСПАНИ</t>
+        </is>
+      </c>
+      <c r="B867" s="18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/3595643240504585</t>
+        </is>
+      </c>
+      <c r="C867" s="18" t="inlineStr">
+        <is>
+          <t>Error_NoPostField</t>
+        </is>
+      </c>
+    </row>
+    <row r="868" ht="25" customHeight="1">
+      <c r="A868" s="12" t="inlineStr">
+        <is>
+          <t>Русскоговорящие девочки Аликанте</t>
+        </is>
+      </c>
+      <c r="B868" s="12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/540744534458042</t>
+        </is>
+      </c>
+      <c r="C868" s="12" t="inlineStr">
         <is>
           <t>Аликанте</t>
-        </is>
-      </c>
-    </row>
-    <row r="868" ht="25" customHeight="1">
-      <c r="A868" s="18" t="inlineStr">
-        <is>
-          <t>ДЕВОЧКИ ИСПАНИ</t>
-        </is>
-      </c>
-      <c r="B868" s="18" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/3595643240504585</t>
-        </is>
-      </c>
-      <c r="C868" s="18" t="inlineStr">
-        <is>
-          <t>Error_NoPostField</t>
         </is>
       </c>
     </row>
     <row r="869" ht="25" customHeight="1">
       <c r="A869" s="12" t="inlineStr">
         <is>
-          <t>Русскоговорящие девочки Аликанте</t>
+          <t>АЛИКАНТЕ, ТОРРЕВЬЕХА - Я ТУТ, В ИСПАНИИ (объявления)</t>
         </is>
       </c>
       <c r="B869" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/540744534458042</t>
+          <t>https://www.facebook.com/groups/559840569302187</t>
         </is>
       </c>
       <c r="C869" s="12" t="inlineStr">
@@ -14615,12 +14615,12 @@
     <row r="870" ht="25" customHeight="1">
       <c r="A870" s="12" t="inlineStr">
         <is>
-          <t>АЛИКАНТЕ, ТОРРЕВЬЕХА - Я ТУТ, В ИСПАНИИ (объявления)</t>
+          <t>Испания. Аликанте - Alicante</t>
         </is>
       </c>
       <c r="B870" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/559840569302187</t>
+          <t>https://www.facebook.com/groups/rusos.en.alicante.ispaniya</t>
         </is>
       </c>
       <c r="C870" s="12" t="inlineStr">
@@ -14632,12 +14632,12 @@
     <row r="871" ht="25" customHeight="1">
       <c r="A871" s="12" t="inlineStr">
         <is>
-          <t>Испания. Аликанте - Alicante</t>
+          <t>✔️ДЕВОЧКИ И МАЛЬЧИКИ АЛИКАНТЕ И ПРИГОРОДЫ! Реклама и общение! Alicante</t>
         </is>
       </c>
       <c r="B871" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/rusos.en.alicante.ispaniya</t>
+          <t>https://www.facebook.com/groups/devochki.alicante</t>
         </is>
       </c>
       <c r="C871" s="12" t="inlineStr">
@@ -14647,48 +14647,48 @@
       </c>
     </row>
     <row r="872" ht="25" customHeight="1">
-      <c r="A872" s="12" t="inlineStr">
-        <is>
-          <t>✔️ДЕВОЧКИ И МАЛЬЧИКИ АЛИКАНТЕ И ПРИГОРОДЫ! Реклама и общение! Alicante</t>
-        </is>
-      </c>
-      <c r="B872" s="12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/devochki.alicante</t>
-        </is>
-      </c>
-      <c r="C872" s="12" t="inlineStr">
+      <c r="A872" s="18" t="inlineStr">
+        <is>
+          <t>Всё для Всех. Аликанте и окрестности</t>
+        </is>
+      </c>
+      <c r="B872" s="18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/257025849899456</t>
+        </is>
+      </c>
+      <c r="C872" s="18" t="inlineStr">
+        <is>
+          <t>Error_NoPostField</t>
+        </is>
+      </c>
+    </row>
+    <row r="873" ht="25" customHeight="1">
+      <c r="A873" s="12" t="inlineStr">
+        <is>
+          <t>АЛИКАНТЕ КОСТА БЛАНКА ИСПАНИЯ ТОП ЛУЧШИХ ОБЪЯВЛЕНИЙ</t>
+        </is>
+      </c>
+      <c r="B873" s="12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/618018532996864</t>
+        </is>
+      </c>
+      <c r="C873" s="12" t="inlineStr">
         <is>
           <t>Аликанте</t>
-        </is>
-      </c>
-    </row>
-    <row r="873" ht="25" customHeight="1">
-      <c r="A873" s="18" t="inlineStr">
-        <is>
-          <t>Всё для Всех. Аликанте и окрестности</t>
-        </is>
-      </c>
-      <c r="B873" s="18" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/257025849899456</t>
-        </is>
-      </c>
-      <c r="C873" s="18" t="inlineStr">
-        <is>
-          <t>Error_NoPostField</t>
         </is>
       </c>
     </row>
     <row r="874" ht="25" customHeight="1">
       <c r="A874" s="12" t="inlineStr">
         <is>
-          <t>АЛИКАНТЕ КОСТА БЛАНКА ИСПАНИЯ ТОП ЛУЧШИХ ОБЪЯВЛЕНИЙ</t>
+          <t>Бесплатные Объявления в Аликанте, Торревьеха, Бенидорм by aDondeVamos</t>
         </is>
       </c>
       <c r="B874" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/618018532996864</t>
+          <t>https://www.facebook.com/groups/212999650068406</t>
         </is>
       </c>
       <c r="C874" s="12" t="inlineStr">
@@ -14700,12 +14700,12 @@
     <row r="875" ht="25" customHeight="1">
       <c r="A875" s="12" t="inlineStr">
         <is>
-          <t>Бесплатные Объявления в Аликанте, Торревьеха, Бенидорм by aDondeVamos</t>
+          <t>Объявления Аликанте (anuncios Alicante)</t>
         </is>
       </c>
       <c r="B875" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/212999650068406</t>
+          <t>https://www.facebook.com/groups/2224817494383562</t>
         </is>
       </c>
       <c r="C875" s="12" t="inlineStr">
@@ -14717,46 +14717,46 @@
     <row r="876" ht="25" customHeight="1">
       <c r="A876" s="12" t="inlineStr">
         <is>
-          <t>Объявления Аликанте (anuncios Alicante)</t>
+          <t>ИСПАНИЯ Мадрид Барселона Валенсия Севилья Аликанте Малага Мурсия Пальма ...</t>
         </is>
       </c>
       <c r="B876" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/2224817494383562</t>
+          <t>https://www.facebook.com/groups/spainchat</t>
         </is>
       </c>
       <c r="C876" s="12" t="inlineStr">
         <is>
-          <t>Аликанте</t>
+          <t>Барселона</t>
         </is>
       </c>
     </row>
     <row r="877" ht="25" customHeight="1">
       <c r="A877" s="12" t="inlineStr">
         <is>
-          <t>ИСПАНИЯ Мадрид Барселона Валенсия Севилья Аликанте Малага Мурсия Пальма ...</t>
+          <t>Аликанте бесплатная доска объявлений</t>
         </is>
       </c>
       <c r="B877" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/spainchat</t>
+          <t>https://www.facebook.com/groups/8217249545068684</t>
         </is>
       </c>
       <c r="C877" s="12" t="inlineStr">
         <is>
-          <t>Барселона</t>
+          <t>Аликанте</t>
         </is>
       </c>
     </row>
     <row r="878" ht="25" customHeight="1">
       <c r="A878" s="12" t="inlineStr">
         <is>
-          <t>Аликанте бесплатная доска объявлений</t>
+          <t>Аликанте�Alicante</t>
         </is>
       </c>
       <c r="B878" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/8217249545068684</t>
+          <t>https://www.facebook.com/groups/956622952080572</t>
         </is>
       </c>
       <c r="C878" s="12" t="inlineStr">
@@ -14768,12 +14768,12 @@
     <row r="879" ht="25" customHeight="1">
       <c r="A879" s="12" t="inlineStr">
         <is>
-          <t>Аликанте�Alicante</t>
+          <t>Доска объявлений Аликанте, Испания</t>
         </is>
       </c>
       <c r="B879" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/956622952080572</t>
+          <t>https://www.facebook.com/groups/449053035293552</t>
         </is>
       </c>
       <c r="C879" s="12" t="inlineStr">
@@ -14785,12 +14785,12 @@
     <row r="880" ht="25" customHeight="1">
       <c r="A880" s="12" t="inlineStr">
         <is>
-          <t>Доска объявлений Аликанте, Испания</t>
+          <t>Аликанте Инфо \ Alicante - Costa Blanca</t>
         </is>
       </c>
       <c r="B880" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/449053035293552</t>
+          <t>https://www.facebook.com/groups/1591440111160802</t>
         </is>
       </c>
       <c r="C880" s="12" t="inlineStr">
@@ -14802,12 +14802,12 @@
     <row r="881" ht="25" customHeight="1">
       <c r="A881" s="12" t="inlineStr">
         <is>
-          <t>Аликанте Инфо \ Alicante - Costa Blanca</t>
+          <t>Аликанте без границ. Объявления, работа, недвижимость, услуги, реклама.</t>
         </is>
       </c>
       <c r="B881" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1591440111160802</t>
+          <t>https://www.facebook.com/groups/547821528743338</t>
         </is>
       </c>
       <c r="C881" s="12" t="inlineStr">
@@ -14819,12 +14819,12 @@
     <row r="882" ht="25" customHeight="1">
       <c r="A882" s="12" t="inlineStr">
         <is>
-          <t>Аликанте без границ. Объявления, работа, недвижимость, услуги, реклама.</t>
+          <t>АЛИКАНТЕ доска объявлений</t>
         </is>
       </c>
       <c r="B882" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/547821528743338</t>
+          <t>https://www.facebook.com/groups/2935197746744290</t>
         </is>
       </c>
       <c r="C882" s="12" t="inlineStr">
@@ -14836,100 +14836,100 @@
     <row r="883" ht="25" customHeight="1">
       <c r="A883" s="12" t="inlineStr">
         <is>
-          <t>АЛИКАНТЕ доска объявлений</t>
+          <t>Афиша ᕗ весь Израиль ᕗ Лучшие мероприятия 🇮🇱</t>
         </is>
       </c>
       <c r="B883" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/2935197746744290</t>
+          <t>https://www.facebook.com/groups/955602182622769</t>
         </is>
       </c>
       <c r="C883" s="12" t="inlineStr">
         <is>
-          <t>Аликанте</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
     <row r="884" ht="25" customHeight="1">
       <c r="A884" s="12" t="inlineStr">
         <is>
-          <t>Афиша ᕗ весь Израиль ᕗ Лучшие мероприятия 🇮🇱</t>
+          <t>ДЕВОЧКИ В АЛИКАНТЕ</t>
         </is>
       </c>
       <c r="B884" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/955602182622769</t>
+          <t>https://www.facebook.com/groups/1221126725506351</t>
         </is>
       </c>
       <c r="C884" s="12" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Аликанте</t>
         </is>
       </c>
     </row>
     <row r="885" ht="25" customHeight="1">
-      <c r="A885" s="12" t="inlineStr">
-        <is>
-          <t>ДЕВОЧКИ В АЛИКАНТЕ</t>
-        </is>
-      </c>
-      <c r="B885" s="12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/1221126725506351</t>
-        </is>
-      </c>
-      <c r="C885" s="12" t="inlineStr">
-        <is>
-          <t>Аликанте</t>
+      <c r="A885" s="11" t="inlineStr">
+        <is>
+          <t>IR RĪGĀ/TusovkaRiga/</t>
+        </is>
+      </c>
+      <c r="B885" s="11" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/tusovkariga</t>
+        </is>
+      </c>
+      <c r="C885" s="11" t="inlineStr">
+        <is>
+          <t>Рига</t>
         </is>
       </c>
     </row>
     <row r="886" ht="25" customHeight="1">
-      <c r="A886" s="11" t="inlineStr">
-        <is>
-          <t>IR RĪGĀ/TusovkaRiga/</t>
-        </is>
-      </c>
-      <c r="B886" s="11" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/tusovkariga</t>
-        </is>
-      </c>
-      <c r="C886" s="11" t="inlineStr">
+      <c r="A886" s="12" t="inlineStr">
+        <is>
+          <t>Cарафан - Рига</t>
+        </is>
+      </c>
+      <c r="B886" s="12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/skidka.na.bileti</t>
+        </is>
+      </c>
+      <c r="C886" s="12" t="inlineStr">
         <is>
           <t>Рига</t>
         </is>
       </c>
     </row>
     <row r="887" ht="25" customHeight="1">
-      <c r="A887" s="12" t="inlineStr">
-        <is>
-          <t>Cарафан - Рига</t>
-        </is>
-      </c>
-      <c r="B887" s="12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/skidka.na.bileti</t>
-        </is>
-      </c>
-      <c r="C887" s="12" t="inlineStr">
+      <c r="A887" s="11" t="inlineStr">
+        <is>
+          <t>Латвия (Рига, Даугавпилс, Лиепая, Елгава, Юрмала, Вентспилс)</t>
+        </is>
+      </c>
+      <c r="B887" s="11" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/in.latvia</t>
+        </is>
+      </c>
+      <c r="C887" s="11" t="inlineStr">
         <is>
           <t>Рига</t>
         </is>
       </c>
     </row>
     <row r="888" ht="25" customHeight="1">
-      <c r="A888" s="11" t="inlineStr">
-        <is>
-          <t>Латвия (Рига, Даугавпилс, Лиепая, Елгава, Юрмала, Вентспилс)</t>
-        </is>
-      </c>
-      <c r="B888" s="11" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/in.latvia</t>
-        </is>
-      </c>
-      <c r="C888" s="11" t="inlineStr">
+      <c r="A888" s="12" t="inlineStr">
+        <is>
+          <t>Объявления Рига🇱🇻🇱🇻🇱🇻</t>
+        </is>
+      </c>
+      <c r="B888" s="12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/981364649142688</t>
+        </is>
+      </c>
+      <c r="C888" s="12" t="inlineStr">
         <is>
           <t>Рига</t>
         </is>
@@ -14938,12 +14938,12 @@
     <row r="889" ht="25" customHeight="1">
       <c r="A889" s="12" t="inlineStr">
         <is>
-          <t>Объявления Рига🇱🇻🇱🇻🇱🇻</t>
+          <t>Рига</t>
         </is>
       </c>
       <c r="B889" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/981364649142688</t>
+          <t>https://www.facebook.com/groups/oldriga</t>
         </is>
       </c>
       <c r="C889" s="12" t="inlineStr">
@@ -14955,12 +14955,12 @@
     <row r="890" ht="25" customHeight="1">
       <c r="A890" s="12" t="inlineStr">
         <is>
-          <t>Рига</t>
+          <t>РЕКЛАМА И ПРОЧЕЕ - РИГА, ЛАТВИЯ</t>
         </is>
       </c>
       <c r="B890" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/oldriga</t>
+          <t>https://www.facebook.com/groups/1156754854334699</t>
         </is>
       </c>
       <c r="C890" s="12" t="inlineStr">
@@ -14972,12 +14972,12 @@
     <row r="891" ht="25" customHeight="1">
       <c r="A891" s="12" t="inlineStr">
         <is>
-          <t>РЕКЛАМА И ПРОЧЕЕ - РИГА, ЛАТВИЯ</t>
+          <t>Рига - доска объявлений</t>
         </is>
       </c>
       <c r="B891" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1156754854334699</t>
+          <t>https://www.facebook.com/groups/reklamalatvia</t>
         </is>
       </c>
       <c r="C891" s="12" t="inlineStr">
@@ -14989,29 +14989,29 @@
     <row r="892" ht="25" customHeight="1">
       <c r="A892" s="12" t="inlineStr">
         <is>
-          <t>Рига - доска объявлений</t>
+          <t>Вильнюс - Все свои!</t>
         </is>
       </c>
       <c r="B892" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/reklamalatvia</t>
+          <t>https://www.facebook.com/groups/russianreklama.litva</t>
         </is>
       </c>
       <c r="C892" s="12" t="inlineStr">
         <is>
-          <t>Рига</t>
+          <t>Вильнюс</t>
         </is>
       </c>
     </row>
     <row r="893" ht="25" customHeight="1">
       <c r="A893" s="12" t="inlineStr">
         <is>
-          <t>Вильнюс - Все свои!</t>
+          <t>🌸 Вильнюс | Между нами, девочками</t>
         </is>
       </c>
       <c r="B893" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/russianreklama.litva</t>
+          <t>https://www.facebook.com/groups/481010253224689</t>
         </is>
       </c>
       <c r="C893" s="12" t="inlineStr">
@@ -15023,12 +15023,12 @@
     <row r="894" ht="25" customHeight="1">
       <c r="A894" s="12" t="inlineStr">
         <is>
-          <t>🌸 Вильнюс | Между нами, девочками</t>
+          <t>Вильнюс - доска объявлений</t>
         </is>
       </c>
       <c r="B894" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/481010253224689</t>
+          <t>https://www.facebook.com/groups/850882665644164</t>
         </is>
       </c>
       <c r="C894" s="12" t="inlineStr">
@@ -15038,65 +15038,65 @@
       </c>
     </row>
     <row r="895" ht="25" customHeight="1">
-      <c r="A895" s="12" t="inlineStr">
-        <is>
-          <t>Вильнюс - доска объявлений</t>
-        </is>
-      </c>
-      <c r="B895" s="12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/850882665644164</t>
-        </is>
-      </c>
-      <c r="C895" s="12" t="inlineStr">
-        <is>
-          <t>Вильнюс</t>
+      <c r="A895" s="18" t="inlineStr">
+        <is>
+          <t>Вильнюс для всех:) /Vilnius dlia vsex:)</t>
+        </is>
+      </c>
+      <c r="B895" s="18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/501702489979518</t>
+        </is>
+      </c>
+      <c r="C895" s="18" t="inlineStr">
+        <is>
+          <t>Error_NoPostField</t>
         </is>
       </c>
     </row>
     <row r="896" ht="25" customHeight="1">
-      <c r="A896" s="18" t="inlineStr">
-        <is>
-          <t>Вильнюс для всех:) /Vilnius dlia vsex:)</t>
-        </is>
-      </c>
-      <c r="B896" s="18" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/501702489979518</t>
-        </is>
-      </c>
-      <c r="C896" s="18" t="inlineStr">
-        <is>
-          <t>Error_NoPostField</t>
+      <c r="A896" s="12" t="inlineStr">
+        <is>
+          <t>ЛИТВА Вильнюс Каунас Клайпеда Шяуляй...</t>
+        </is>
+      </c>
+      <c r="B896" s="12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/lithuaniachat</t>
+        </is>
+      </c>
+      <c r="C896" s="12" t="inlineStr">
+        <is>
+          <t>Литва</t>
         </is>
       </c>
     </row>
     <row r="897" ht="25" customHeight="1">
       <c r="A897" s="12" t="inlineStr">
         <is>
-          <t>ЛИТВА Вильнюс Каунас Клайпеда Шяуляй...</t>
+          <t>Русскоязычный Вильнюс / Vilnius</t>
         </is>
       </c>
       <c r="B897" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/lithuaniachat</t>
+          <t>https://www.facebook.com/groups/vilnius1323</t>
         </is>
       </c>
       <c r="C897" s="12" t="inlineStr">
         <is>
-          <t>Литва</t>
+          <t>Вильнюс</t>
         </is>
       </c>
     </row>
     <row r="898" ht="25" customHeight="1">
       <c r="A898" s="12" t="inlineStr">
         <is>
-          <t>Русскоязычный Вильнюс / Vilnius</t>
+          <t>Русскоговорящий Вильнюс / Russian speaking Vilnius</t>
         </is>
       </c>
       <c r="B898" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/vilnius1323</t>
+          <t>https://www.facebook.com/groups/258215618884603</t>
         </is>
       </c>
       <c r="C898" s="12" t="inlineStr">
@@ -15108,12 +15108,12 @@
     <row r="899" ht="25" customHeight="1">
       <c r="A899" s="12" t="inlineStr">
         <is>
-          <t>Русскоговорящий Вильнюс / Russian speaking Vilnius</t>
+          <t>Объявления Вильнюс</t>
         </is>
       </c>
       <c r="B899" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/258215618884603</t>
+          <t>https://www.facebook.com/groups/rusvilnius</t>
         </is>
       </c>
       <c r="C899" s="12" t="inlineStr">
@@ -15125,46 +15125,46 @@
     <row r="900" ht="25" customHeight="1">
       <c r="A900" s="12" t="inlineStr">
         <is>
-          <t>Объявления Вильнюс</t>
+          <t>ОБЪЯВЛЕНИЯ Литва Вильнюс Каунас Клайпеда...</t>
         </is>
       </c>
       <c r="B900" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/rusvilnius</t>
+          <t>https://www.facebook.com/groups/1061546074400060</t>
         </is>
       </c>
       <c r="C900" s="12" t="inlineStr">
         <is>
-          <t>Вильнюс</t>
+          <t>Литва</t>
         </is>
       </c>
     </row>
     <row r="901" ht="25" customHeight="1">
       <c r="A901" s="12" t="inlineStr">
         <is>
-          <t>ОБЪЯВЛЕНИЯ Литва Вильнюс Каунас Клайпеда...</t>
+          <t>Наш Вильнюс</t>
         </is>
       </c>
       <c r="B901" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1061546074400060</t>
+          <t>https://www.facebook.com/groups/656310325066277</t>
         </is>
       </c>
       <c r="C901" s="12" t="inlineStr">
         <is>
-          <t>Литва</t>
+          <t>Вильнюс</t>
         </is>
       </c>
     </row>
     <row r="902" ht="25" customHeight="1">
       <c r="A902" s="12" t="inlineStr">
         <is>
-          <t>Наш Вильнюс</t>
+          <t>Vilnius šiandien / Vilnius today / Вильнюс сегодня</t>
         </is>
       </c>
       <c r="B902" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/656310325066277</t>
+          <t>https://www.facebook.com/groups/1239332713098790</t>
         </is>
       </c>
       <c r="C902" s="12" t="inlineStr">
@@ -15174,48 +15174,48 @@
       </c>
     </row>
     <row r="903" ht="25" customHeight="1">
-      <c r="A903" s="12" t="inlineStr">
-        <is>
-          <t>Vilnius šiandien / Vilnius today / Вильнюс сегодня</t>
-        </is>
-      </c>
-      <c r="B903" s="12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/1239332713098790</t>
-        </is>
-      </c>
-      <c r="C903" s="12" t="inlineStr">
+      <c r="A903" s="18" t="inlineStr">
+        <is>
+          <t>Вильнюс, Литва, Новости события.</t>
+        </is>
+      </c>
+      <c r="B903" s="18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/VilniusOnline</t>
+        </is>
+      </c>
+      <c r="C903" s="18" t="inlineStr">
+        <is>
+          <t>Error_NoPostField</t>
+        </is>
+      </c>
+    </row>
+    <row r="904" ht="25" customHeight="1">
+      <c r="A904" s="12" t="inlineStr">
+        <is>
+          <t>Просто Вильнюс</t>
+        </is>
+      </c>
+      <c r="B904" s="12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/simplevilnius</t>
+        </is>
+      </c>
+      <c r="C904" s="12" t="inlineStr">
         <is>
           <t>Вильнюс</t>
-        </is>
-      </c>
-    </row>
-    <row r="904" ht="25" customHeight="1">
-      <c r="A904" s="18" t="inlineStr">
-        <is>
-          <t>Вильнюс, Литва, Новости события.</t>
-        </is>
-      </c>
-      <c r="B904" s="18" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/VilniusOnline</t>
-        </is>
-      </c>
-      <c r="C904" s="18" t="inlineStr">
-        <is>
-          <t>Error_NoPostField</t>
         </is>
       </c>
     </row>
     <row r="905" ht="25" customHeight="1">
       <c r="A905" s="12" t="inlineStr">
         <is>
-          <t>Просто Вильнюс</t>
+          <t>Про Вильнюс и не только</t>
         </is>
       </c>
       <c r="B905" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/simplevilnius</t>
+          <t>https://www.facebook.com/groups/vilniaby</t>
         </is>
       </c>
       <c r="C905" s="12" t="inlineStr">
@@ -15227,46 +15227,46 @@
     <row r="906" ht="25" customHeight="1">
       <c r="A906" s="12" t="inlineStr">
         <is>
-          <t>Про Вильнюс и не только</t>
+          <t>БЕСПЛАТНЫЕ ОБЪЯВЛЕНИЯ Литва Вильнюс Каунас...</t>
         </is>
       </c>
       <c r="B906" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/vilniaby</t>
+          <t>https://www.facebook.com/groups/683985412190387</t>
         </is>
       </c>
       <c r="C906" s="12" t="inlineStr">
         <is>
-          <t>Вильнюс</t>
+          <t>Литва</t>
         </is>
       </c>
     </row>
     <row r="907" ht="25" customHeight="1">
       <c r="A907" s="12" t="inlineStr">
         <is>
-          <t>БЕСПЛАТНЫЕ ОБЪЯВЛЕНИЯ Литва Вильнюс Каунас...</t>
+          <t>Вильнюс, Литва (Vilnius, Lietuva)</t>
         </is>
       </c>
       <c r="B907" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/683985412190387</t>
+          <t>https://www.facebook.com/groups/vilniuschat</t>
         </is>
       </c>
       <c r="C907" s="12" t="inlineStr">
         <is>
-          <t>Литва</t>
+          <t>Вильнюс</t>
         </is>
       </c>
     </row>
     <row r="908" ht="25" customHeight="1">
       <c r="A908" s="12" t="inlineStr">
         <is>
-          <t>Вильнюс, Литва (Vilnius, Lietuva)</t>
+          <t>Koncertai vilniuje | концерты в вильнюсе</t>
         </is>
       </c>
       <c r="B908" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/vilniuschat</t>
+          <t>https://www.facebook.com/groups/2069855259992406</t>
         </is>
       </c>
       <c r="C908" s="12" t="inlineStr">
@@ -15276,31 +15276,31 @@
       </c>
     </row>
     <row r="909" ht="25" customHeight="1">
-      <c r="A909" s="12" t="inlineStr">
-        <is>
-          <t>Koncertai vilniuje | концерты в вильнюсе</t>
-        </is>
-      </c>
-      <c r="B909" s="12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/2069855259992406</t>
-        </is>
-      </c>
-      <c r="C909" s="12" t="inlineStr">
-        <is>
-          <t>Вильнюс</t>
+      <c r="A909" s="18" t="inlineStr">
+        <is>
+          <t>Русские Вильнюсa</t>
+        </is>
+      </c>
+      <c r="B909" s="18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1134049106952237</t>
+        </is>
+      </c>
+      <c r="C909" s="18" t="inlineStr">
+        <is>
+          <t>Error_NoPostField</t>
         </is>
       </c>
     </row>
     <row r="910" ht="25" customHeight="1">
       <c r="A910" s="18" t="inlineStr">
         <is>
-          <t>Русские Вильнюсa</t>
+          <t>Русскоязычные жители Литвы</t>
         </is>
       </c>
       <c r="B910" s="18" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1134049106952237</t>
+          <t>https://www.facebook.com/groups/russians.lt</t>
         </is>
       </c>
       <c r="C910" s="18" t="inlineStr">
@@ -15310,31 +15310,31 @@
       </c>
     </row>
     <row r="911" ht="25" customHeight="1">
-      <c r="A911" s="18" t="inlineStr">
-        <is>
-          <t>Русскоязычные жители Литвы</t>
-        </is>
-      </c>
-      <c r="B911" s="18" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/russians.lt</t>
-        </is>
-      </c>
-      <c r="C911" s="18" t="inlineStr">
-        <is>
-          <t>Error_NoPostField</t>
+      <c r="A911" s="12" t="inlineStr">
+        <is>
+          <t>[vilniusobjavlenija]</t>
+        </is>
+      </c>
+      <c r="B911" s="12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/vilniusobjavlenija</t>
+        </is>
+      </c>
+      <c r="C911" s="12" t="inlineStr">
+        <is>
+          <t>Литва</t>
         </is>
       </c>
     </row>
     <row r="912" ht="25" customHeight="1">
       <c r="A912" s="12" t="inlineStr">
         <is>
-          <t>[vilniusobjavlenija]</t>
+          <t>Русские в Литве</t>
         </is>
       </c>
       <c r="B912" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/vilniusobjavlenija</t>
+          <t>https://www.facebook.com/groups/207243089736749</t>
         </is>
       </c>
       <c r="C912" s="12" t="inlineStr">
@@ -15346,12 +15346,12 @@
     <row r="913" ht="25" customHeight="1">
       <c r="A913" s="12" t="inlineStr">
         <is>
-          <t>Русские в Литве</t>
+          <t>Русскоязычные в Литве</t>
         </is>
       </c>
       <c r="B913" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/207243089736749</t>
+          <t>https://www.facebook.com/groups/1117096982102019</t>
         </is>
       </c>
       <c r="C913" s="12" t="inlineStr">
@@ -15363,12 +15363,12 @@
     <row r="914" ht="25" customHeight="1">
       <c r="A914" s="12" t="inlineStr">
         <is>
-          <t>Русскоязычные в Литве</t>
+          <t>Русскоязычная Литва</t>
         </is>
       </c>
       <c r="B914" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1117096982102019</t>
+          <t>https://www.facebook.com/groups/242649104544714</t>
         </is>
       </c>
       <c r="C914" s="12" t="inlineStr">
@@ -15380,12 +15380,12 @@
     <row r="915" ht="25" customHeight="1">
       <c r="A915" s="12" t="inlineStr">
         <is>
-          <t>Русскоязычная Литва</t>
+          <t>RU/LT: русскоязычное комьюнити в Литве</t>
         </is>
       </c>
       <c r="B915" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/242649104544714</t>
+          <t>https://www.facebook.com/groups/rulit</t>
         </is>
       </c>
       <c r="C915" s="12" t="inlineStr">
@@ -15397,97 +15397,97 @@
     <row r="916" ht="25" customHeight="1">
       <c r="A916" s="12" t="inlineStr">
         <is>
-          <t>RU/LT: русскоязычное комьюнити в Литве</t>
+          <t>Нужный справочник Вильнюса</t>
         </is>
       </c>
       <c r="B916" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/rulit</t>
+          <t>https://www.facebook.com/groups/575393717414600</t>
         </is>
       </c>
       <c r="C916" s="12" t="inlineStr">
         <is>
-          <t>Литва</t>
+          <t>Вильнюс</t>
         </is>
       </c>
     </row>
     <row r="917" ht="25" customHeight="1">
       <c r="A917" s="12" t="inlineStr">
         <is>
-          <t>Нужный справочник Вильнюса</t>
+          <t>[451394615036766]</t>
         </is>
       </c>
       <c r="B917" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/575393717414600</t>
+          <t>https://www.facebook.com/groups/451394615036766</t>
         </is>
       </c>
       <c r="C917" s="12" t="inlineStr">
         <is>
-          <t>Вильнюс</t>
+          <t>Таллинн</t>
         </is>
       </c>
     </row>
     <row r="918" ht="25" customHeight="1">
       <c r="A918" s="12" t="inlineStr">
         <is>
-          <t>[451394615036766]</t>
+          <t>[2203785133184131]</t>
         </is>
       </c>
       <c r="B918" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/451394615036766</t>
+          <t>https://www.facebook.com/groups/2203785133184131</t>
         </is>
       </c>
       <c r="C918" s="12" t="inlineStr">
         <is>
-          <t>Таллинн</t>
+          <t>Латвия</t>
         </is>
       </c>
     </row>
     <row r="919" ht="25" customHeight="1">
       <c r="A919" s="12" t="inlineStr">
         <is>
-          <t>[2203785133184131]</t>
+          <t>[1048970433935629]</t>
         </is>
       </c>
       <c r="B919" s="12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/2203785133184131</t>
+          <t>https://www.facebook.com/groups/1048970433935629</t>
         </is>
       </c>
       <c r="C919" s="12" t="inlineStr">
         <is>
-          <t>Латвия</t>
+          <t>Литва</t>
         </is>
       </c>
     </row>
     <row r="920" ht="25" customHeight="1">
-      <c r="A920" s="12" t="inlineStr">
-        <is>
-          <t>[1048970433935629]</t>
-        </is>
-      </c>
-      <c r="B920" s="12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/1048970433935629</t>
-        </is>
-      </c>
-      <c r="C920" s="12" t="inlineStr">
-        <is>
-          <t>Литва</t>
+      <c r="A920" s="19" t="inlineStr">
+        <is>
+          <t>Культурная жизнь Израиля</t>
+        </is>
+      </c>
+      <c r="B920" s="19" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/lifeinisrael/</t>
+        </is>
+      </c>
+      <c r="C920" s="19" t="inlineStr">
+        <is>
+          <t>Тест_Директ</t>
         </is>
       </c>
     </row>
     <row r="921" ht="25" customHeight="1">
       <c r="A921" s="19" t="inlineStr">
         <is>
-          <t>Культурная жизнь Израиля</t>
+          <t>Где погулять в Израиле? Отзывы, Рекомендации рестораны, экскурсии</t>
         </is>
       </c>
       <c r="B921" s="19" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/lifeinisrael/</t>
+          <t>https://www.facebook.com/groups/turizmil/</t>
         </is>
       </c>
       <c r="C921" s="19" t="inlineStr">
@@ -15499,12 +15499,12 @@
     <row r="922" ht="25" customHeight="1">
       <c r="A922" s="19" t="inlineStr">
         <is>
-          <t>Где погулять в Израиле? Отзывы, Рекомендации рестораны, экскурсии</t>
+          <t>Творчество Израиль 🇮🇱🎵🎭</t>
         </is>
       </c>
       <c r="B922" s="19" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/turizmil/</t>
+          <t>https://www.facebook.com/groups/329697607612317/</t>
         </is>
       </c>
       <c r="C922" s="19" t="inlineStr">
@@ -15513,23 +15513,7 @@
         </is>
       </c>
     </row>
-    <row r="923" ht="25" customHeight="1">
-      <c r="A923" s="19" t="inlineStr">
-        <is>
-          <t>Творчество Израиль 🇮🇱🎵🎭</t>
-        </is>
-      </c>
-      <c r="B923" s="19" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/329697607612317/</t>
-        </is>
-      </c>
-      <c r="C923" s="19" t="inlineStr">
-        <is>
-          <t>Тест_Директ</t>
-        </is>
-      </c>
-    </row>
+    <row r="923" ht="25" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Page_Bard/groups.xlsx
+++ b/Page_Bard/groups.xlsx
@@ -117,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -160,6 +160,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -527,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C922"/>
+  <dimension ref="A1:C939"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -15513,7 +15519,295 @@
         </is>
       </c>
     </row>
-    <row r="923" ht="25" customHeight="1"/>
+    <row r="923" ht="25" customHeight="1">
+      <c r="A923" s="20" t="inlineStr">
+        <is>
+          <t>Девочки. Израиль.</t>
+        </is>
+      </c>
+      <c r="B923" s="20" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/897192168462907/</t>
+        </is>
+      </c>
+      <c r="C923" s="20" t="inlineStr">
+        <is>
+          <t>Event 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" s="20" t="inlineStr">
+        <is>
+          <t>Клуб любителей театра и кино в Израиле</t>
+        </is>
+      </c>
+      <c r="B924" s="20" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1084611341608897/</t>
+        </is>
+      </c>
+      <c r="C924" s="20" t="inlineStr">
+        <is>
+          <t>Event 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" s="20" t="inlineStr">
+        <is>
+          <t>BILETY.CO.IL – агрегатор билетов на спектакли и концерты в Израиле.</t>
+        </is>
+      </c>
+      <c r="B925" s="20" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/weekend.il/</t>
+        </is>
+      </c>
+      <c r="C925" s="20" t="inlineStr">
+        <is>
+          <t>Event 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="20" t="inlineStr">
+        <is>
+          <t>Израиль-повседневная жизнь.</t>
+        </is>
+      </c>
+      <c r="B926" s="20" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1628212920761200/</t>
+        </is>
+      </c>
+      <c r="C926" s="20" t="inlineStr">
+        <is>
+          <t>Event 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="20" t="inlineStr">
+        <is>
+          <t>Афиша в Израиле 🎯</t>
+        </is>
+      </c>
+      <c r="B927" s="20" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/afishail/</t>
+        </is>
+      </c>
+      <c r="C927" s="20" t="inlineStr">
+        <is>
+          <t>Event 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="20" t="inlineStr">
+        <is>
+          <t>Что и Где, Когда и Как</t>
+        </is>
+      </c>
+      <c r="B928" s="20" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1633214516929486/</t>
+        </is>
+      </c>
+      <c r="C928" s="20" t="inlineStr">
+        <is>
+          <t>Event 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="20" t="inlineStr">
+        <is>
+          <t>Рекомендации (המלצות): на блюдечке с голубой каёмочкой</t>
+        </is>
+      </c>
+      <c r="B929" s="20" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/267673493681466/</t>
+        </is>
+      </c>
+      <c r="C929" s="20" t="inlineStr">
+        <is>
+          <t>Event 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="20" t="inlineStr">
+        <is>
+          <t>Стильные ДевчОнки בנות בסטייל</t>
+        </is>
+      </c>
+      <c r="B930" s="20" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1842049746034969/</t>
+        </is>
+      </c>
+      <c r="C930" s="20" t="inlineStr">
+        <is>
+          <t>Event 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="20" t="inlineStr">
+        <is>
+          <t>Events&amp;Shows Israel</t>
+        </is>
+      </c>
+      <c r="B931" s="20" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/2058582517693314/</t>
+        </is>
+      </c>
+      <c r="C931" s="20" t="inlineStr">
+        <is>
+          <t>Event 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="20" t="inlineStr">
+        <is>
+          <t>Новенькие, вам рады!</t>
+        </is>
+      </c>
+      <c r="B932" s="20" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1563295877305603/</t>
+        </is>
+      </c>
+      <c r="C932" s="20" t="inlineStr">
+        <is>
+          <t>Event 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="21" t="inlineStr">
+        <is>
+          <t>Израиль - отдыхающий !!!</t>
+        </is>
+      </c>
+      <c r="B933" s="21" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/377680662301500</t>
+        </is>
+      </c>
+      <c r="C933" s="21" t="inlineStr">
+        <is>
+          <t>Event 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="21" t="inlineStr">
+        <is>
+          <t>Горские евреи в душе</t>
+        </is>
+      </c>
+      <c r="B934" s="21" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/855081021528572</t>
+        </is>
+      </c>
+      <c r="C934" s="21" t="inlineStr">
+        <is>
+          <t>Event 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" s="21" t="inlineStr">
+        <is>
+          <t>Потому, что Девочки🧡Израиль</t>
+        </is>
+      </c>
+      <c r="B935" s="21" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/Devochky</t>
+        </is>
+      </c>
+      <c r="C935" s="21" t="inlineStr">
+        <is>
+          <t>Event 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" s="21" t="inlineStr">
+        <is>
+          <t>Горские Евреи В Душе❤️ קווקזים ב נשמה</t>
+        </is>
+      </c>
+      <c r="B936" s="21" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1002220399830433</t>
+        </is>
+      </c>
+      <c r="C936" s="21" t="inlineStr">
+        <is>
+          <t>Event 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" s="21" t="inlineStr">
+        <is>
+          <t>Горские Евреи всего мира❤️</t>
+        </is>
+      </c>
+      <c r="B937" s="21" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/2457430481025501</t>
+        </is>
+      </c>
+      <c r="C937" s="21" t="inlineStr">
+        <is>
+          <t>Event 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" s="21" t="inlineStr">
+        <is>
+          <t>Куда бы деться на Софаш</t>
+        </is>
+      </c>
+      <c r="B938" s="21" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/sofash</t>
+        </is>
+      </c>
+      <c r="C938" s="21" t="inlineStr">
+        <is>
+          <t>Event 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="21" t="inlineStr">
+        <is>
+          <t>Афиша ᕗ весь Израиль ᕗ Лучшие мероприятия 🇮🇱</t>
+        </is>
+      </c>
+      <c r="B939" s="21" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/955602182622769</t>
+        </is>
+      </c>
+      <c r="C939" s="21" t="inlineStr">
+        <is>
+          <t>Event 2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Page_Bard/groups.xlsx
+++ b/Page_Bard/groups.xlsx
@@ -117,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -166,6 +166,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -533,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C939"/>
+  <dimension ref="A1:C984"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -15808,6 +15811,771 @@
         </is>
       </c>
     </row>
+    <row r="940">
+      <c r="A940" s="22" t="inlineStr">
+        <is>
+          <t>Беер-Шева - Доска объявлений</t>
+        </is>
+      </c>
+      <c r="B940" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1079488720984819/</t>
+        </is>
+      </c>
+      <c r="C940" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="22" t="inlineStr">
+        <is>
+          <t>Беер-шева на русском</t>
+        </is>
+      </c>
+      <c r="B941" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/769207001226730/</t>
+        </is>
+      </c>
+      <c r="C941" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="22" t="inlineStr">
+        <is>
+          <t>РАБОТА БЕЕР ШЕВА И НЕГЕВ</t>
+        </is>
+      </c>
+      <c r="B942" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/384591369128704/</t>
+        </is>
+      </c>
+      <c r="C942" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="22" t="inlineStr">
+        <is>
+          <t>ИЗРАИЛЬ Тель-Авив Назарет Хайфа Рамла Иерусалим Беэр-Шева Ариэль Ашдод ...</t>
+        </is>
+      </c>
+      <c r="B943" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/israeltalk/</t>
+        </is>
+      </c>
+      <c r="C943" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="22" t="inlineStr">
+        <is>
+          <t>Только Беэр-Шева, Купи-Продай-Сними-Отдай.</t>
+        </is>
+      </c>
+      <c r="B944" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/BeerShevaKupiProdaySnimiOtday/</t>
+        </is>
+      </c>
+      <c r="C944" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="22" t="inlineStr">
+        <is>
+          <t>Новости Беэр-Шевы и юга Израиля 🔵</t>
+        </is>
+      </c>
+      <c r="B945" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/657430564424423/</t>
+        </is>
+      </c>
+      <c r="C945" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="22" t="inlineStr">
+        <is>
+          <t>Беэр шева и юг Израиля -  ты не один! ❤️❤️❤️</t>
+        </is>
+      </c>
+      <c r="B946" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/696712835346644/</t>
+        </is>
+      </c>
+      <c r="C946" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" s="22" t="inlineStr">
+        <is>
+          <t>Берите Даром! Беэр Шева</t>
+        </is>
+      </c>
+      <c r="B947" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/992703217816981/</t>
+        </is>
+      </c>
+      <c r="C947" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева . Поиск работы и работников.</t>
+        </is>
+      </c>
+      <c r="B948" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/833157560218142/</t>
+        </is>
+      </c>
+      <c r="C948" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="22" t="inlineStr">
+        <is>
+          <t>Интресное в Беэр Шеве на юге  Израиля и другие новости</t>
+        </is>
+      </c>
+      <c r="B949" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/154106369975405/</t>
+        </is>
+      </c>
+      <c r="C949" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="22" t="inlineStr">
+        <is>
+          <t>Отдаю. Продаю. Покупаю. Меняю. Беер Шева и Южный округ</t>
+        </is>
+      </c>
+      <c r="B950" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/159443707839213/</t>
+        </is>
+      </c>
+      <c r="C950" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="22" t="inlineStr">
+        <is>
+          <t>Со вторых рук - Беэр Шева и окрестности</t>
+        </is>
+      </c>
+      <c r="B951" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/891250204344295/</t>
+        </is>
+      </c>
+      <c r="C951" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="22" t="inlineStr">
+        <is>
+          <t>Русскоязычная Беэр Шева и Негев</t>
+        </is>
+      </c>
+      <c r="B952" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/769112478734041/</t>
+        </is>
+      </c>
+      <c r="C952" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="22" t="inlineStr">
+        <is>
+          <t>✏ Работа и услуги в Беер Шеве ⒿⓄⒷ</t>
+        </is>
+      </c>
+      <c r="B953" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/JobBeerShevaRus/</t>
+        </is>
+      </c>
+      <c r="C953" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="22" t="inlineStr">
+        <is>
+          <t>🇮🇱🌴Беэр Шева .Без выгоды !!! Негев.🌴🇮🇱</t>
+        </is>
+      </c>
+      <c r="B954" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/167643897441850/</t>
+        </is>
+      </c>
+      <c r="C954" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева Онлайн</t>
+        </is>
+      </c>
+      <c r="B955" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/955891061192257/</t>
+        </is>
+      </c>
+      <c r="C955" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="22" t="inlineStr">
+        <is>
+          <t>Беэр-Шева_ОбО!ВсЕм!</t>
+        </is>
+      </c>
+      <c r="B956" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/606972704227133/</t>
+        </is>
+      </c>
+      <c r="C956" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="22" t="inlineStr">
+        <is>
+          <t>Аренда и продажа квартир в Беер Шева</t>
+        </is>
+      </c>
+      <c r="B957" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RentBuySaleBeerSheva/</t>
+        </is>
+      </c>
+      <c r="C957" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева. Израиль</t>
+        </is>
+      </c>
+      <c r="B958" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/647623481002896/</t>
+        </is>
+      </c>
+      <c r="C958" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="22" t="inlineStr">
+        <is>
+          <t>Работа в Беер-Шева</t>
+        </is>
+      </c>
+      <c r="B959" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/2702623196743741/</t>
+        </is>
+      </c>
+      <c r="C959" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="22" t="inlineStr">
+        <is>
+          <t>Работа в Беер-Шева - встань и иди</t>
+        </is>
+      </c>
+      <c r="B960" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1262638579043139/</t>
+        </is>
+      </c>
+      <c r="C960" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="22" t="inlineStr">
+        <is>
+          <t>Квартиры Продажа/сьем Беер Шева, Димона, Ерухам</t>
+        </is>
+      </c>
+      <c r="B961" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/810882429079262/</t>
+        </is>
+      </c>
+      <c r="C961" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="22" t="inlineStr">
+        <is>
+          <t>АРЕНДА И ПРОДАЖА КВАРТИР БЕЭР-ШЕВА דירות להשכרה בבאר שבע</t>
+        </is>
+      </c>
+      <c r="B962" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/2675390616117313/</t>
+        </is>
+      </c>
+      <c r="C962" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="22" t="inlineStr">
+        <is>
+          <t>юг,беер шева.</t>
+        </is>
+      </c>
+      <c r="B963" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/227342391341468/</t>
+        </is>
+      </c>
+      <c r="C963" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="22" t="inlineStr">
+        <is>
+          <t>Беэр-шева и негев, Будьте как Дома!</t>
+        </is>
+      </c>
+      <c r="B964" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1076500926302328/</t>
+        </is>
+      </c>
+      <c r="C964" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="22" t="inlineStr">
+        <is>
+          <t>באר שבע והנגב - כולנו יחד!Беэр Шева и Негев- ВСЕ вместе!</t>
+        </is>
+      </c>
+      <c r="B965" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/372140643156123/</t>
+        </is>
+      </c>
+      <c r="C965" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="22" t="inlineStr">
+        <is>
+          <t>Работа в Беер-Шева</t>
+        </is>
+      </c>
+      <c r="B966" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/869242735551599/</t>
+        </is>
+      </c>
+      <c r="C966" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="22" t="inlineStr">
+        <is>
+          <t>🧩 Лучшая работа  Беэр-Шева</t>
+        </is>
+      </c>
+      <c r="B967" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/5883403265038875/</t>
+        </is>
+      </c>
+      <c r="C967" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="22" t="inlineStr">
+        <is>
+          <t>Беер-Шева, часик в радость - работа в Беер-Шева</t>
+        </is>
+      </c>
+      <c r="B968" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1410217233785863/</t>
+        </is>
+      </c>
+      <c r="C968" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="22" t="inlineStr">
+        <is>
+          <t>לוח דירות בבאר שבע/ Квартиры в Беэр Шеве</t>
+        </is>
+      </c>
+      <c r="B969" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/beershevanadlan/</t>
+        </is>
+      </c>
+      <c r="C969" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="22" t="inlineStr">
+        <is>
+          <t>Бесплатная Реклама ( Беэр шева, Ашдод, Кирьят Гат, Реховот, Ришон, и др. .</t>
+        </is>
+      </c>
+      <c r="B970" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1030665935011986/</t>
+        </is>
+      </c>
+      <c r="C970" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" s="22" t="inlineStr">
+        <is>
+          <t>Беер-шева.ru Новости юга Израиля</t>
+        </is>
+      </c>
+      <c r="B971" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1494682433908767/</t>
+        </is>
+      </c>
+      <c r="C971" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="22" t="inlineStr">
+        <is>
+          <t>Беер-Шева - Бесплатная доска объявлений и реклама</t>
+        </is>
+      </c>
+      <c r="B972" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1037267152298907/</t>
+        </is>
+      </c>
+      <c r="C972" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="22" t="inlineStr">
+        <is>
+          <t>Беер шева и  всё что с ней связано</t>
+        </is>
+      </c>
+      <c r="B973" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/211368689416964/</t>
+        </is>
+      </c>
+      <c r="C973" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="22" t="inlineStr">
+        <is>
+          <t>Доска объявлений Беер-Шева</t>
+        </is>
+      </c>
+      <c r="B974" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/312503512735671/</t>
+        </is>
+      </c>
+      <c r="C974" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="22" t="inlineStr">
+        <is>
+          <t>Дорога домой (Беер Шева и негев !!!רק באר שבע ונגב !!) помощь животным</t>
+        </is>
+      </c>
+      <c r="B975" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/161168908008760/</t>
+        </is>
+      </c>
+      <c r="C975" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="22" t="inlineStr">
+        <is>
+          <t>שכונת נחל עשן - Беэр-Шева</t>
+        </is>
+      </c>
+      <c r="B976" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1128663622499357/</t>
+        </is>
+      </c>
+      <c r="C976" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="22" t="inlineStr">
+        <is>
+          <t>שכונה יא באר-שבע - Район Юд-алеф, Беэр-Шева</t>
+        </is>
+      </c>
+      <c r="B977" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1040542456846299/</t>
+        </is>
+      </c>
+      <c r="C977" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="22" t="inlineStr">
+        <is>
+          <t>Ремонты в Беэр-Шеве, Ашкелоне и Ашдоде</t>
+        </is>
+      </c>
+      <c r="B978" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1598374683815087/</t>
+        </is>
+      </c>
+      <c r="C978" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" s="22" t="inlineStr">
+        <is>
+          <t>Работа Беер-Шева - Добро пожаловать</t>
+        </is>
+      </c>
+      <c r="B979" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/4441805966143398/</t>
+        </is>
+      </c>
+      <c r="C979" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="22" t="inlineStr">
+        <is>
+          <t>Беэр-Шева</t>
+        </is>
+      </c>
+      <c r="B980" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/457400318364107/</t>
+        </is>
+      </c>
+      <c r="C980" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" s="22" t="inlineStr">
+        <is>
+          <t>Иерусалим-Бейт Шемеш-Модиин. Поиск работы Тель авив Ашдод, Беер Шева, Хайфа</t>
+        </is>
+      </c>
+      <c r="B981" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/poiskrabotnikov/</t>
+        </is>
+      </c>
+      <c r="C981" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="22" t="inlineStr">
+        <is>
+          <t>БЕЭР-ШЕВА-УЧЕБА-БИЗНЕС-УСЛУГИ-ТОВАРЫ🎯</t>
+        </is>
+      </c>
+      <c r="B982" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/beer.sheva.7/</t>
+        </is>
+      </c>
+      <c r="C982" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" s="22" t="inlineStr">
+        <is>
+          <t>Квартиры Продажа/сьем Беер Шева, Димона, Ерухам</t>
+        </is>
+      </c>
+      <c r="B983" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/279796709117194/</t>
+        </is>
+      </c>
+      <c r="C983" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" s="22" t="inlineStr">
+        <is>
+          <t>Беэр-Шева Работа | Вакансии | Поиск и резюме</t>
+        </is>
+      </c>
+      <c r="B984" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1270773640995656/</t>
+        </is>
+      </c>
+      <c r="C984" s="22" t="inlineStr">
+        <is>
+          <t>Беэр Шева</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Page_Bard/groups.xlsx
+++ b/Page_Bard/groups.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C984"/>
+  <dimension ref="A1:C1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -16576,6 +16576,278 @@
         </is>
       </c>
     </row>
+    <row r="985">
+      <c r="A985" s="22" t="inlineStr">
+        <is>
+          <t>Аликанте Работа Знакомства Обьявления</t>
+        </is>
+      </c>
+      <c r="B985" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1247083042126031/</t>
+        </is>
+      </c>
+      <c r="C985" s="22" t="inlineStr">
+        <is>
+          <t>Аликанте</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="22" t="inlineStr">
+        <is>
+          <t>Солнечный Аликанте/ Sunny Alicante</t>
+        </is>
+      </c>
+      <c r="B986" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/395426747211233/</t>
+        </is>
+      </c>
+      <c r="C986" s="22" t="inlineStr">
+        <is>
+          <t>Аликанте</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="22" t="inlineStr">
+        <is>
+          <t>Мир Аликанте • Alicante</t>
+        </is>
+      </c>
+      <c r="B987" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1396258483817388/</t>
+        </is>
+      </c>
+      <c r="C987" s="22" t="inlineStr">
+        <is>
+          <t>Аликанте</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="22" t="inlineStr">
+        <is>
+          <t>Аликанте услуги</t>
+        </is>
+      </c>
+      <c r="B988" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/793464015014372/</t>
+        </is>
+      </c>
+      <c r="C988" s="22" t="inlineStr">
+        <is>
+          <t>Аликанте</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" s="22" t="inlineStr">
+        <is>
+          <t>Аликанте 📢 ОБЪЯВЛЕНИЯ</t>
+        </is>
+      </c>
+      <c r="B989" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1862983711177404/</t>
+        </is>
+      </c>
+      <c r="C989" s="22" t="inlineStr">
+        <is>
+          <t>Аликанте</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" s="22" t="inlineStr">
+        <is>
+          <t>Объявления Испания: Барселона, Валенсия, Аликанте, Торревьеха, Малага.</t>
+        </is>
+      </c>
+      <c r="B990" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/949331247070892/</t>
+        </is>
+      </c>
+      <c r="C990" s="22" t="inlineStr">
+        <is>
+          <t>Испания</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" s="22" t="inlineStr">
+        <is>
+          <t>Реклама Аликанте</t>
+        </is>
+      </c>
+      <c r="B991" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/121793429936458/</t>
+        </is>
+      </c>
+      <c r="C991" s="22" t="inlineStr">
+        <is>
+          <t>Аликанте</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" s="22" t="inlineStr">
+        <is>
+          <t>Аликанте - сказочный отдых!</t>
+        </is>
+      </c>
+      <c r="B992" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1531118960439297/</t>
+        </is>
+      </c>
+      <c r="C992" s="22" t="inlineStr">
+        <is>
+          <t>Аликанте</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" s="22" t="inlineStr">
+        <is>
+          <t>Испания Аликанте Барахолка</t>
+        </is>
+      </c>
+      <c r="B993" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/341797922845430/</t>
+        </is>
+      </c>
+      <c r="C993" s="22" t="inlineStr">
+        <is>
+          <t>Аликанте</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" s="22" t="inlineStr">
+        <is>
+          <t>Аликанте Сегодня - новостной портал Аликанте на русском языке</t>
+        </is>
+      </c>
+      <c r="B994" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/alicantetoday/</t>
+        </is>
+      </c>
+      <c r="C994" s="22" t="inlineStr">
+        <is>
+          <t>Аликанте</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" s="22" t="inlineStr">
+        <is>
+          <t>Испания, Аликанте - Продаю/Покупаю.</t>
+        </is>
+      </c>
+      <c r="B995" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/565600561023455/</t>
+        </is>
+      </c>
+      <c r="C995" s="22" t="inlineStr">
+        <is>
+          <t>Аликанте</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" s="22" t="inlineStr">
+        <is>
+          <t>Мамы и папы в Аликанте</t>
+        </is>
+      </c>
+      <c r="B996" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/229346674147778/</t>
+        </is>
+      </c>
+      <c r="C996" s="22" t="inlineStr">
+        <is>
+          <t>Аликанте</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" s="22" t="inlineStr">
+        <is>
+          <t>Торревьеха Аликанте Гвардемар Дения Алтея По русски👍🏼</t>
+        </is>
+      </c>
+      <c r="B997" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/679334608836265/</t>
+        </is>
+      </c>
+      <c r="C997" s="22" t="inlineStr">
+        <is>
+          <t>Аликанте</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" s="22" t="inlineStr">
+        <is>
+          <t>Услуги и работа в Аликанте. Русскоязычная группа.</t>
+        </is>
+      </c>
+      <c r="B998" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/6769236433195039/</t>
+        </is>
+      </c>
+      <c r="C998" s="22" t="inlineStr">
+        <is>
+          <t>Аликанте</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" s="22" t="inlineStr">
+        <is>
+          <t>ОБЪЯВЛЕНИЯ ‼️‼️‼️ АЛИКАНТЕ - БЕНИДОРМ- ВАЛЕНСИЯ ‼️‼️‼️</t>
+        </is>
+      </c>
+      <c r="B999" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/625627860270677/</t>
+        </is>
+      </c>
+      <c r="C999" s="22" t="inlineStr">
+        <is>
+          <t>Аликанте</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="22" t="inlineStr">
+        <is>
+          <t>Услуги в Аликанте</t>
+        </is>
+      </c>
+      <c r="B1000" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/461064077415596/</t>
+        </is>
+      </c>
+      <c r="C1000" s="22" t="inlineStr">
+        <is>
+          <t>Аликанте</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Page_Bard/groups.xlsx
+++ b/Page_Bard/groups.xlsx
@@ -11349,7 +11349,7 @@
       </c>
       <c r="C665" s="12" t="inlineStr">
         <is>
-          <t>Лондон</t>
+          <t>Error_NoPostField</t>
         </is>
       </c>
     </row>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C710" s="12" t="inlineStr">
         <is>
-          <t>Лондон</t>
+          <t>Error_NoPostField</t>
         </is>
       </c>
     </row>

--- a/Page_Bard/groups.xlsx
+++ b/Page_Bard/groups.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1000"/>
+  <dimension ref="A1:C1019"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -16848,6 +16848,329 @@
         </is>
       </c>
     </row>
+    <row r="1001">
+      <c r="A1001" s="22" t="inlineStr">
+        <is>
+          <t>Испания без границ</t>
+        </is>
+      </c>
+      <c r="B1001" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/236281803443931/</t>
+        </is>
+      </c>
+      <c r="C1001" s="22" t="inlineStr">
+        <is>
+          <t>Испания</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="22" t="inlineStr">
+        <is>
+          <t>Испания для нас (все объявления БЕСПЛАТНО)</t>
+        </is>
+      </c>
+      <c r="B1002" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/268985041533048/</t>
+        </is>
+      </c>
+      <c r="C1002" s="22" t="inlineStr">
+        <is>
+          <t>Испания</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="22" t="inlineStr">
+        <is>
+          <t>Доска объявлений Испании</t>
+        </is>
+      </c>
+      <c r="B1003" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/480778534615491/</t>
+        </is>
+      </c>
+      <c r="C1003" s="22" t="inlineStr">
+        <is>
+          <t>Испания</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="22" t="inlineStr">
+        <is>
+          <t>ИСПАНИЯ 🌴🥘🍷</t>
+        </is>
+      </c>
+      <c r="B1004" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/154170115283429/</t>
+        </is>
+      </c>
+      <c r="C1004" s="22" t="inlineStr">
+        <is>
+          <t>Испания</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="22" t="inlineStr">
+        <is>
+          <t>Испания для Вас</t>
+        </is>
+      </c>
+      <c r="B1005" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/278527195651360/</t>
+        </is>
+      </c>
+      <c r="C1005" s="22" t="inlineStr">
+        <is>
+          <t>Испания</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="22" t="inlineStr">
+        <is>
+          <t>Реклама и объявления в Испании</t>
+        </is>
+      </c>
+      <c r="B1006" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/4ru.publicidad/</t>
+        </is>
+      </c>
+      <c r="C1006" s="22" t="inlineStr">
+        <is>
+          <t>Испания</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="22" t="inlineStr">
+        <is>
+          <t>Доска объявлений в Испании ⚜️</t>
+        </is>
+      </c>
+      <c r="B1007" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/ukrruvalencia/</t>
+        </is>
+      </c>
+      <c r="C1007" s="22" t="inlineStr">
+        <is>
+          <t>Испания</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="22" t="inlineStr">
+        <is>
+          <t>Объявления и Реклама в Испании</t>
+        </is>
+      </c>
+      <c r="B1008" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/advinspain/</t>
+        </is>
+      </c>
+      <c r="C1008" s="22" t="inlineStr">
+        <is>
+          <t>Испания</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="22" t="inlineStr">
+        <is>
+          <t>Испания. Доска бесплатных объявлений Elcontacto.ru</t>
+        </is>
+      </c>
+      <c r="B1009" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/adsspain/</t>
+        </is>
+      </c>
+      <c r="C1009" s="22" t="inlineStr">
+        <is>
+          <t>Испания</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="22" t="inlineStr">
+        <is>
+          <t>Торревьеха Бланка</t>
+        </is>
+      </c>
+      <c r="B1010" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/778037859303863/</t>
+        </is>
+      </c>
+      <c r="C1010" s="22" t="inlineStr">
+        <is>
+          <t>Аликанте</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="22" t="inlineStr">
+        <is>
+          <t>NRW КЕЛЬН Бонн Дюссельдорф Wuppertal KÖLN BONN Українці Русские Беларусы</t>
+        </is>
+      </c>
+      <c r="B1011" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/uaruby/</t>
+        </is>
+      </c>
+      <c r="C1011" s="22" t="inlineStr">
+        <is>
+          <t>Кёльн</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="22" t="inlineStr">
+        <is>
+          <t>Не скучаем в Кельне</t>
+        </is>
+      </c>
+      <c r="B1012" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/215876405212737/</t>
+        </is>
+      </c>
+      <c r="C1012" s="22" t="inlineStr">
+        <is>
+          <t>Кёльн</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="22" t="inlineStr">
+        <is>
+          <t>RUNRW | Русскоязычные в NRW | Кельн Дюссельдорф Дортмунд Эссен Дюйсбург</t>
+        </is>
+      </c>
+      <c r="B1013" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RussianNRW/</t>
+        </is>
+      </c>
+      <c r="C1013" s="22" t="inlineStr">
+        <is>
+          <t>Кёльн</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="22" t="inlineStr">
+        <is>
+          <t>Бонн, Кельн, Bonn, Köln. Наши в Бонне. Наши в Кельне</t>
+        </is>
+      </c>
+      <c r="B1014" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/344462437702090/</t>
+        </is>
+      </c>
+      <c r="C1014" s="22" t="inlineStr">
+        <is>
+          <t>Кёльн</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="22" t="inlineStr">
+        <is>
+          <t>Русскоязычные в Кёльне</t>
+        </is>
+      </c>
+      <c r="B1015" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/russeninkoeln/</t>
+        </is>
+      </c>
+      <c r="C1015" s="22" t="inlineStr">
+        <is>
+          <t>Кёльн</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="22" t="inlineStr">
+        <is>
+          <t>Даугавпилс - Рига - Вильнюс / Daugavpils - Riga - Vilnius (попутчики)</t>
+        </is>
+      </c>
+      <c r="B1016" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/887972583119094/</t>
+        </is>
+      </c>
+      <c r="C1016" s="22" t="inlineStr">
+        <is>
+          <t>Рига</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="22" t="inlineStr">
+        <is>
+          <t>Литва Вильнюс Каунас Клайпеда Панявежис Шяуляй Алитус Lithuania</t>
+        </is>
+      </c>
+      <c r="B1017" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RussianLithuania/</t>
+        </is>
+      </c>
+      <c r="C1017" s="22" t="inlineStr">
+        <is>
+          <t>Литва</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="22" t="inlineStr">
+        <is>
+          <t>МОЯ РИГА</t>
+        </is>
+      </c>
+      <c r="B1018" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1179716898805863/</t>
+        </is>
+      </c>
+      <c r="C1018" s="22" t="inlineStr">
+        <is>
+          <t>Рига</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="22" t="inlineStr">
+        <is>
+          <t>Ашдод - по русски 2</t>
+        </is>
+      </c>
+      <c r="B1019" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/336966036742161/</t>
+        </is>
+      </c>
+      <c r="C1019" s="22" t="inlineStr">
+        <is>
+          <t>Ашдод</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Page_Bard/groups.xlsx
+++ b/Page_Bard/groups.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1019"/>
+  <dimension ref="A1:C1043"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -17171,6 +17171,414 @@
         </is>
       </c>
     </row>
+    <row r="1020">
+      <c r="A1020" s="22" t="inlineStr">
+        <is>
+          <t>БГ-ХЕЛП ЛОНДОН</t>
+        </is>
+      </c>
+      <c r="B1020" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/126675055939723/</t>
+        </is>
+      </c>
+      <c r="C1020" s="22" t="inlineStr">
+        <is>
+          <t>Лондон 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="22" t="inlineStr">
+        <is>
+          <t>АНГЛИЯ | Новости, oбъявления, работа, жилье в Лондоне</t>
+        </is>
+      </c>
+      <c r="B1021" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/england.news.advert.job.house.rent/</t>
+        </is>
+      </c>
+      <c r="C1021" s="22" t="inlineStr">
+        <is>
+          <t>Лондон 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="22" t="inlineStr">
+        <is>
+          <t>обяви Лондон</t>
+        </is>
+      </c>
+      <c r="B1022" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1671258022904963/</t>
+        </is>
+      </c>
+      <c r="C1022" s="22" t="inlineStr">
+        <is>
+          <t>Лондон 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="22" t="inlineStr">
+        <is>
+          <t>ЛОНДОН- БГ ХЕЛП</t>
+        </is>
+      </c>
+      <c r="B1023" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/398299661461105/</t>
+        </is>
+      </c>
+      <c r="C1023" s="22" t="inlineStr">
+        <is>
+          <t>Лондон 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="22" t="inlineStr">
+        <is>
+          <t>Обяви Лондон</t>
+        </is>
+      </c>
+      <c r="B1024" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1009099949205524/</t>
+        </is>
+      </c>
+      <c r="C1024" s="22" t="inlineStr">
+        <is>
+          <t>Лондон 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="22" t="inlineStr">
+        <is>
+          <t>Наши в Лондоне - Робота Жилье Услуги</t>
+        </is>
+      </c>
+      <c r="B1025" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/244847707906981/</t>
+        </is>
+      </c>
+      <c r="C1025" s="22" t="inlineStr">
+        <is>
+          <t>Лондон 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="22" t="inlineStr">
+        <is>
+          <t>Обяви Лондон</t>
+        </is>
+      </c>
+      <c r="B1026" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/obiavilondon/</t>
+        </is>
+      </c>
+      <c r="C1026" s="22" t="inlineStr">
+        <is>
+          <t>Лондон 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="22" t="inlineStr">
+        <is>
+          <t>Лондон по-нашому, Англія (Ukrainians, London, England)</t>
+        </is>
+      </c>
+      <c r="B1027" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/londonponashomu/</t>
+        </is>
+      </c>
+      <c r="C1027" s="22" t="inlineStr">
+        <is>
+          <t>Лондон 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="22" t="inlineStr">
+        <is>
+          <t>Лондон</t>
+        </is>
+      </c>
+      <c r="B1028" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/158762847623967/</t>
+        </is>
+      </c>
+      <c r="C1028" s="22" t="inlineStr">
+        <is>
+          <t>Лондон 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="22" t="inlineStr">
+        <is>
+          <t>Лондон - Англія - Оголошення</t>
+        </is>
+      </c>
+      <c r="B1029" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/5992024727546127/</t>
+        </is>
+      </c>
+      <c r="C1029" s="22" t="inlineStr">
+        <is>
+          <t>Лондон 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="22" t="inlineStr">
+        <is>
+          <t>Доска Объявлений Лондон</t>
+        </is>
+      </c>
+      <c r="B1030" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/2424938907835471/</t>
+        </is>
+      </c>
+      <c r="C1030" s="22" t="inlineStr">
+        <is>
+          <t>Лондон 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="22" t="inlineStr">
+        <is>
+          <t>Русскоговорящие в London ( Russian speakers in London )</t>
+        </is>
+      </c>
+      <c r="B1031" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1534976066768785/</t>
+        </is>
+      </c>
+      <c r="C1031" s="22" t="inlineStr">
+        <is>
+          <t>Лондон 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="22" t="inlineStr">
+        <is>
+          <t>Russians in London | Русские в Лондоне</t>
+        </is>
+      </c>
+      <c r="B1032" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/838970723769036/</t>
+        </is>
+      </c>
+      <c r="C1032" s="22" t="inlineStr">
+        <is>
+          <t>Лондон 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="22" t="inlineStr">
+        <is>
+          <t>Жизнь Восточного Лондона (East London)</t>
+        </is>
+      </c>
+      <c r="B1033" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/797286882069924/</t>
+        </is>
+      </c>
+      <c r="C1033" s="22" t="inlineStr">
+        <is>
+          <t>Лондон 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="22" t="inlineStr">
+        <is>
+          <t>Наш Лондон 🇬🇧🫶</t>
+        </is>
+      </c>
+      <c r="B1034" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/450560866744845/</t>
+        </is>
+      </c>
+      <c r="C1034" s="22" t="inlineStr">
+        <is>
+          <t>Лондон 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="22" t="inlineStr">
+        <is>
+          <t>Русские мамы в Лондоне</t>
+        </is>
+      </c>
+      <c r="B1035" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/316721102820184/</t>
+        </is>
+      </c>
+      <c r="C1035" s="22" t="inlineStr">
+        <is>
+          <t>Лондон 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="22" t="inlineStr">
+        <is>
+          <t>Лондон-Англия-Объявления</t>
+        </is>
+      </c>
+      <c r="B1036" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1525093397774204/</t>
+        </is>
+      </c>
+      <c r="C1036" s="22" t="inlineStr">
+        <is>
+          <t>Лондон 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="22" t="inlineStr">
+        <is>
+          <t>Великобритания</t>
+        </is>
+      </c>
+      <c r="B1037" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RussianBritania/</t>
+        </is>
+      </c>
+      <c r="C1037" s="22" t="inlineStr">
+        <is>
+          <t>Лондон 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="22" t="inlineStr">
+        <is>
+          <t>Наши в Англии (Great Britain)</t>
+        </is>
+      </c>
+      <c r="B1038" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/nashivanglii/</t>
+        </is>
+      </c>
+      <c r="C1038" s="22" t="inlineStr">
+        <is>
+          <t>Лондон 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="22" t="inlineStr">
+        <is>
+          <t>Русскоязычные В Англии И Зарубежом</t>
+        </is>
+      </c>
+      <c r="B1039" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1025108274177027/</t>
+        </is>
+      </c>
+      <c r="C1039" s="22" t="inlineStr">
+        <is>
+          <t>Лондон 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="22" t="inlineStr">
+        <is>
+          <t>Русский Форум в Англии</t>
+        </is>
+      </c>
+      <c r="B1040" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/286834915839554/</t>
+        </is>
+      </c>
+      <c r="C1040" s="22" t="inlineStr">
+        <is>
+          <t>Лондон 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="22" t="inlineStr">
+        <is>
+          <t>Наши в Великобритании, Англии</t>
+        </is>
+      </c>
+      <c r="B1041" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/233522196227996/</t>
+        </is>
+      </c>
+      <c r="C1041" s="22" t="inlineStr">
+        <is>
+          <t>Лондон 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="22" t="inlineStr">
+        <is>
+          <t>Русскоговорящие в Англии (Russians in England)</t>
+        </is>
+      </c>
+      <c r="B1042" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RussiaInEngland/</t>
+        </is>
+      </c>
+      <c r="C1042" s="22" t="inlineStr">
+        <is>
+          <t>Лондон 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="22" t="inlineStr">
+        <is>
+          <t>Доска Объявлений в Англии</t>
+        </is>
+      </c>
+      <c r="B1043" s="22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/199672256779044/</t>
+        </is>
+      </c>
+      <c r="C1043" s="22" t="inlineStr">
+        <is>
+          <t>Лондон 2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Page_Bard/groups.xlsx
+++ b/Page_Bard/groups.xlsx
@@ -16385,7 +16385,7 @@
       </c>
       <c r="C973" s="22" t="inlineStr">
         <is>
-          <t>Беэр Шева</t>
+          <t>Error_NoPostField</t>
         </is>
       </c>
     </row>
@@ -16419,7 +16419,7 @@
       </c>
       <c r="C975" s="22" t="inlineStr">
         <is>
-          <t>Беэр Шева</t>
+          <t>Error_NoPostField</t>
         </is>
       </c>
     </row>
@@ -16521,7 +16521,7 @@
       </c>
       <c r="C981" s="22" t="inlineStr">
         <is>
-          <t>Беэр Шева</t>
+          <t>Error_NoPostField</t>
         </is>
       </c>
     </row>

--- a/Page_Bard/groups.xlsx
+++ b/Page_Bard/groups.xlsx
@@ -11961,7 +11961,7 @@
       </c>
       <c r="C701" s="12" t="inlineStr">
         <is>
-          <t>Лондон</t>
+          <t>Error_NoPostField</t>
         </is>
       </c>
     </row>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="C702" s="12" t="inlineStr">
         <is>
-          <t>Лондон</t>
+          <t>Error_NoPostField</t>
         </is>
       </c>
     </row>
